--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/Stocks/Data/Stocks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE85E417-1D62-A04C-B29D-EC646EF7EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9B665F-1F69-C147-8FD4-2B704A7A0AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -1176,20 +1176,19 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet1"/>
+      <sheetName val="1. List_AutomaticData"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="C3">
-            <v>205.37</v>
+            <v>278.39</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1617,7 +1616,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$3</f>
-        <v>205.37</v>
+        <v>278.39</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1637,7 +1636,7 @@
       </c>
       <c r="C9" s="94">
         <f>C3*'Statement Q'!J138</f>
-        <v>334753.10000000003</v>
+        <v>453775.69999999995</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">

--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9B665F-1F69-C147-8FD4-2B704A7A0AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72BD642-7E06-8F4E-8DD4-4454A9F7314A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -376,9 +376,6 @@
     <t>Q</t>
   </si>
   <si>
-    <t>Q1 2024</t>
-  </si>
-  <si>
     <t>Q1 2025</t>
   </si>
   <si>
@@ -649,9 +646,6 @@
     <t>29.06.2024</t>
   </si>
   <si>
-    <t>30.03.2024</t>
-  </si>
-  <si>
     <t>Income from discontinued operations</t>
   </si>
   <si>
@@ -704,6 +698,12 @@
   </si>
   <si>
     <t>Net debt</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>28.03.2026</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1184,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="C3">
-            <v>278.39</v>
+            <v>405.47500000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -1607,16 +1607,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$3</f>
-        <v>278.39</v>
+        <v>405.47500000000002</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1632,16 +1632,16 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C9" s="94">
         <f>C3*'Statement Q'!J138</f>
-        <v>453775.69999999995</v>
+        <v>661329.72500000009</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -1656,12 +1656,11 @@
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31.5" style="9" customWidth="1"/>
-    <col min="3" max="4" width="12" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="10.83203125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="12" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="10.83203125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="10.83203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="10" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="12" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="12" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="10" width="10.83203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -1674,34 +1673,34 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1755,7 +1754,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="57" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="17" t="s">
         <v>8</v>
@@ -1791,7 +1790,7 @@
         <v>34639</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
@@ -1826,9 +1825,9 @@
         <v>16456</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="27">
         <v>0</v>
@@ -1861,7 +1860,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="57" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="17" t="s">
         <v>10</v>
@@ -1907,7 +1906,7 @@
         <v>17152</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
         <v>11</v>
       </c>
@@ -1942,7 +1941,7 @@
         <v>8091</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
@@ -1977,9 +1976,9 @@
         <v>4144</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="27">
         <v>0</v>
@@ -2012,9 +2011,9 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="27">
         <v>0</v>
@@ -2047,7 +2046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>13</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>7</v>
       </c>
@@ -2117,7 +2116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
         <v>14</v>
       </c>
@@ -2162,7 +2161,7 @@
         <v>13458</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="57" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="17" t="s">
         <v>15</v>
@@ -2198,7 +2197,7 @@
         <v>3694</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="12" t="s">
         <v>52</v>
       </c>
@@ -2233,9 +2232,9 @@
         <v>-131</v>
       </c>
     </row>
-    <row r="18" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C18" s="27">
         <v>80</v>
@@ -2268,7 +2267,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="19" spans="1:22" s="57" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="17" t="s">
         <v>16</v>
@@ -2304,10 +2303,10 @@
         <v>4140</v>
       </c>
     </row>
-    <row r="20" spans="1:22" s="56" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" s="56" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="27">
         <v>-39</v>
@@ -2350,9 +2349,9 @@
       <c r="U20" s="7"/>
       <c r="V20" s="7"/>
     </row>
-    <row r="21" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="27">
         <v>-10</v>
@@ -2385,7 +2384,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="57" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" s="57" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="17" t="s">
         <v>18</v>
@@ -2421,7 +2420,7 @@
         <v>4269</v>
       </c>
     </row>
-    <row r="23" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="12" t="s">
         <v>17</v>
       </c>
@@ -2456,10 +2455,10 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:22" s="37" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" s="37" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" s="35">
         <v>-498</v>
@@ -2492,7 +2491,7 @@
         <v>4335</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="12" t="s">
         <v>19</v>
       </c>
@@ -2527,7 +2526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
@@ -2562,7 +2561,7 @@
         <v>4335</v>
       </c>
     </row>
-    <row r="27" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="12" t="s">
         <v>21</v>
       </c>
@@ -2597,7 +2596,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="12" t="s">
         <v>22</v>
       </c>
@@ -2632,7 +2631,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="12" t="s">
         <v>23</v>
       </c>
@@ -2667,7 +2666,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="30" spans="1:22" s="16" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" s="16" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="10" t="s">
         <v>24</v>
@@ -2703,7 +2702,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="31" spans="1:22" s="16" customFormat="1" ht="17" collapsed="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" s="16" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="6"/>
       <c r="F31" s="6"/>
@@ -2756,7 +2755,7 @@
     </row>
     <row r="34" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C34" s="27">
         <v>0</v>
@@ -2861,7 +2860,7 @@
     </row>
     <row r="37" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C37" s="27">
         <v>32</v>
@@ -2896,7 +2895,7 @@
     </row>
     <row r="38" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" s="27">
         <v>63</v>
@@ -3037,7 +3036,7 @@
     </row>
     <row r="42" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C42" s="27">
         <v>0</v>
@@ -3107,7 +3106,7 @@
     </row>
     <row r="44" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C44" s="27">
         <v>0</v>
@@ -3142,7 +3141,7 @@
     </row>
     <row r="45" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C45" s="27">
         <v>59</v>
@@ -3399,7 +3398,7 @@
     </row>
     <row r="52" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B52" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C52" s="27">
         <v>383</v>
@@ -3434,7 +3433,7 @@
     </row>
     <row r="53" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C53" s="27">
         <v>391</v>
@@ -3504,7 +3503,7 @@
     </row>
     <row r="55" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B55" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C55" s="27">
         <v>63</v>
@@ -3610,7 +3609,7 @@
     </row>
     <row r="58" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B58" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C58" s="27">
         <v>0</v>
@@ -3645,7 +3644,7 @@
     </row>
     <row r="59" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B59" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C59" s="27">
         <v>0</v>
@@ -3842,7 +3841,7 @@
     </row>
     <row r="64" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B64" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C64" s="27">
         <v>8334</v>
@@ -3877,7 +3876,7 @@
     </row>
     <row r="65" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B65" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="27">
         <v>-119</v>
@@ -4178,7 +4177,7 @@
     </row>
     <row r="75" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B75" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C75" s="27">
         <v>-146</v>
@@ -4213,7 +4212,7 @@
     </row>
     <row r="76" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C76" s="27">
         <v>1</v>
@@ -4248,7 +4247,7 @@
     </row>
     <row r="77" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C77" s="27">
         <v>0</v>
@@ -4318,7 +4317,7 @@
     </row>
     <row r="79" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B79" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C79" s="27">
         <v>0</v>
@@ -4353,7 +4352,7 @@
     </row>
     <row r="80" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C80" s="27">
         <v>11</v>
@@ -4388,7 +4387,7 @@
     </row>
     <row r="81" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B81" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="27">
         <v>86</v>
@@ -4423,7 +4422,7 @@
     </row>
     <row r="82" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B82" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C82" s="27">
         <v>21</v>
@@ -4458,7 +4457,7 @@
     </row>
     <row r="83" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B83" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C83" s="27">
         <v>0</v>
@@ -4493,7 +4492,7 @@
     </row>
     <row r="84" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C84" s="27">
         <v>0</v>
@@ -4528,7 +4527,7 @@
     </row>
     <row r="85" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C85" s="27">
         <v>68</v>
@@ -4563,7 +4562,7 @@
     </row>
     <row r="86" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B86" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C86" s="27">
         <v>0</v>
@@ -4598,7 +4597,7 @@
     </row>
     <row r="87" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B87" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C87" s="27">
         <v>240</v>
@@ -4633,7 +4632,7 @@
     </row>
     <row r="88" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B88" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C88" s="27">
         <v>0</v>
@@ -4668,7 +4667,7 @@
     </row>
     <row r="89" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B89" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C89" s="27">
         <v>0</v>
@@ -4843,7 +4842,7 @@
     </row>
     <row r="94" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B94" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C94" s="27">
         <v>1</v>
@@ -4878,7 +4877,7 @@
     </row>
     <row r="95" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B95" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C95" s="27">
         <v>-163</v>
@@ -4913,7 +4912,7 @@
     </row>
     <row r="96" spans="2:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B96" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C96" s="27">
         <v>138</v>
@@ -4948,7 +4947,7 @@
     </row>
     <row r="97" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B97" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C97" s="27">
         <v>0</v>
@@ -5054,7 +5053,7 @@
     </row>
     <row r="100" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B100" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C100" s="27">
         <v>342</v>
@@ -5089,7 +5088,7 @@
     </row>
     <row r="101" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B101" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C101" s="27">
         <v>0</v>
@@ -5159,7 +5158,7 @@
     </row>
     <row r="103" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B103" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C103" s="27">
         <v>0</v>
@@ -5194,7 +5193,7 @@
     </row>
     <row r="104" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B104" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C104" s="27">
         <v>0</v>
@@ -5229,7 +5228,7 @@
     </row>
     <row r="105" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B105" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C105" s="27">
         <v>0</v>
@@ -5264,7 +5263,7 @@
     </row>
     <row r="106" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B106" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C106" s="27">
         <v>0</v>
@@ -5299,7 +5298,7 @@
     </row>
     <row r="107" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B107" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C107" s="27">
         <v>0</v>
@@ -5334,7 +5333,7 @@
     </row>
     <row r="108" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B108" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C108" s="27">
         <v>0</v>
@@ -5369,7 +5368,7 @@
     </row>
     <row r="109" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B109" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C109" s="27">
         <v>10</v>
@@ -5510,7 +5509,7 @@
     </row>
     <row r="113" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B113" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C113" s="27">
         <v>667</v>
@@ -5545,7 +5544,7 @@
     </row>
     <row r="114" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B114" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C114" s="27">
         <v>782</v>
@@ -5580,7 +5579,7 @@
     </row>
     <row r="115" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B115" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C115" s="27">
         <v>20</v>
@@ -5615,7 +5614,7 @@
     </row>
     <row r="116" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B116" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C116" s="27">
         <v>-230</v>
@@ -5685,7 +5684,7 @@
     </row>
     <row r="118" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B118" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C118" s="27">
         <v>0</v>
@@ -5720,7 +5719,7 @@
     </row>
     <row r="119" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B119" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C119" s="27">
         <v>0</v>
@@ -5755,7 +5754,7 @@
     </row>
     <row r="120" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B120" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C120" s="27">
         <v>0</v>
@@ -6831,7 +6830,7 @@
     </row>
     <row r="149" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B149" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C149" s="30">
         <v>0</v>
@@ -6866,7 +6865,7 @@
     </row>
     <row r="150" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B150" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C150" s="27">
         <v>71</v>
@@ -6901,7 +6900,7 @@
     </row>
     <row r="151" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B151" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C151" s="27">
         <v>62</v>
@@ -6936,7 +6935,7 @@
     </row>
     <row r="152" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B152" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C152" s="91">
         <f>(C20)/C19</f>
@@ -6981,7 +6980,7 @@
     </row>
     <row r="153" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B153" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C153" s="27">
         <v>8200</v>
@@ -7021,10 +7020,10 @@
     <row r="156" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4"/>
       <c r="B156" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A157" s="7"/>
       <c r="B157" s="17" t="s">
         <v>8</v>
@@ -7070,7 +7069,7 @@
         <v>0.34337793290672874</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B158" s="9" t="s">
         <v>9</v>
       </c>
@@ -7112,7 +7111,7 @@
         <v>0.35842826481756646</v>
       </c>
     </row>
-    <row r="159" spans="1:12" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A159" s="7"/>
       <c r="B159" s="17" t="s">
         <v>10</v>
@@ -7158,7 +7157,7 @@
         <v>0.34789783889980352</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B160" s="9" t="s">
         <v>11</v>
       </c>
@@ -7200,7 +7199,7 @@
         <v>0.25325278810408924</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B161" s="12" t="s">
         <v>12</v>
       </c>
@@ -7242,7 +7241,7 @@
         <v>0.4890406036651096</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B162" s="12" t="s">
         <v>14</v>
       </c>
@@ -7287,7 +7286,7 @@
         <v>0.24323325635103926</v>
       </c>
     </row>
-    <row r="163" spans="1:12" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A163" s="7"/>
       <c r="B163" s="17" t="s">
         <v>15</v>
@@ -7330,7 +7329,7 @@
         <v>0.9442105263157895</v>
       </c>
     </row>
-    <row r="164" spans="1:12" s="83" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" s="83" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A164" s="7"/>
       <c r="B164" s="84" t="s">
         <v>16</v>
@@ -7376,7 +7375,7 @@
         <v>1.0814479638009049</v>
       </c>
     </row>
-    <row r="165" spans="1:12" s="83" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" s="83" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A165" s="7"/>
       <c r="B165" s="84" t="s">
         <v>18</v>
@@ -7422,18 +7421,18 @@
         <v>1.6014625228519195</v>
       </c>
     </row>
-    <row r="166" spans="1:12" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B166" s="1"/>
     </row>
     <row r="167" spans="1:12" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4"/>
       <c r="B167" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B168" s="9" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B168" s="9" t="s">
-        <v>115</v>
       </c>
       <c r="C168" s="81">
         <f t="shared" ref="C168:L168" si="30">C8/C5</f>
@@ -7476,9 +7475,9 @@
         <v>0.49516441005802708</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B169" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C169" s="81">
         <f t="shared" ref="C169:L169" si="31">C16/C5</f>
@@ -7521,10 +7520,10 @@
         <v>0.10664280146655504</v>
       </c>
     </row>
-    <row r="170" spans="1:12" s="90" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" s="90" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C170" s="89">
         <f t="shared" ref="C170:L170" si="32">C22/C5</f>
@@ -7567,7 +7566,7 @@
         <v>0.12324258783452179</v>
       </c>
     </row>
-    <row r="171" spans="1:12" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B171" s="1"/>
     </row>
   </sheetData>
@@ -7583,15 +7582,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEB41336-2E39-7442-9864-91E9B0A07818}">
-  <dimension ref="A1:S150"/>
+  <dimension ref="A1:S149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" outlineLevelRow="2" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="9" customWidth="1"/>
-    <col min="3" max="3" width="12" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="12" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="10" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="12" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="10" width="10.83203125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="2" style="1" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="10.33203125" style="1" customWidth="1" outlineLevel="1"/>
     <col min="13" max="13" width="2.33203125" style="1" customWidth="1"/>
@@ -7612,28 +7610,28 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>174</v>
       </c>
       <c r="I2" s="40" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="J2" s="40" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -7651,28 +7649,28 @@
         <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>91</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="40" t="s">
         <v>93</v>
       </c>
       <c r="I3" s="40" t="s">
-        <v>94</v>
+        <v>186</v>
       </c>
       <c r="J3" s="40" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
@@ -7681,14 +7679,14 @@
       <c r="O3" s="4"/>
       <c r="P3" s="51" t="str">
         <f>I3</f>
-        <v>Q3 2025</v>
+        <v>Q4 2025</v>
       </c>
       <c r="Q3" s="5" t="str">
         <f>J3</f>
-        <v>Q4 2025</v>
+        <v>Q1 2026</v>
       </c>
       <c r="R3" s="52" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S3" s="4"/>
     </row>
@@ -7701,137 +7699,137 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O4" s="4"/>
       <c r="P4" s="95" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="96"/>
       <c r="R4" s="97"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="55">
-        <v>5473</v>
+        <v>5835</v>
       </c>
       <c r="D5" s="55">
-        <v>5835</v>
+        <v>6819</v>
       </c>
       <c r="E5" s="55">
-        <v>6819</v>
+        <v>7658</v>
       </c>
       <c r="F5" s="55">
-        <v>7658</v>
+        <v>7438</v>
       </c>
       <c r="G5" s="55">
-        <v>7438</v>
+        <v>7685</v>
       </c>
       <c r="H5" s="55">
-        <v>7685</v>
+        <v>9246</v>
       </c>
       <c r="I5" s="55">
-        <v>9246</v>
+        <v>10270</v>
       </c>
       <c r="J5" s="55">
-        <v>10270</v>
+        <v>10253</v>
       </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
       <c r="N5" s="63">
         <f t="shared" ref="N5:N26" si="0">SUM(G5:J5)</f>
-        <v>34639</v>
+        <v>37454</v>
       </c>
       <c r="O5" s="7"/>
       <c r="P5" s="73">
         <f t="shared" ref="P5:P30" si="1">I5</f>
-        <v>9246</v>
+        <v>10270</v>
       </c>
       <c r="Q5" s="58">
         <f t="shared" ref="Q5:Q30" si="2">J5</f>
-        <v>10270</v>
+        <v>10253</v>
       </c>
       <c r="R5" s="69">
         <f t="shared" ref="R5:R30" si="3">IF(P5=0,
 IF(Q5=0,0,IF(Q5&gt;0,1,-1)),
 (Q5-P5)/ABS(P5)
 )</f>
-        <v>0.11075059485182782</v>
+        <v>-1.6553067185978579E-3</v>
       </c>
       <c r="S5" s="7"/>
     </row>
-    <row r="6" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="27">
-        <v>2683</v>
+        <v>2740</v>
       </c>
       <c r="D6" s="27">
-        <v>2740</v>
+        <v>3167</v>
       </c>
       <c r="E6" s="27">
-        <v>3167</v>
+        <v>3524</v>
       </c>
       <c r="F6" s="27">
-        <v>3524</v>
+        <v>3451</v>
       </c>
       <c r="G6" s="27">
-        <v>3451</v>
+        <v>4366</v>
       </c>
       <c r="H6" s="27">
-        <v>4366</v>
+        <v>4206</v>
       </c>
       <c r="I6" s="27">
-        <v>4206</v>
+        <v>4433</v>
       </c>
       <c r="J6" s="27">
-        <v>4433</v>
+        <v>4576</v>
       </c>
       <c r="K6" s="36"/>
       <c r="L6" s="36"/>
       <c r="M6" s="36"/>
       <c r="N6" s="42">
         <f>SUM(G6:J6)</f>
-        <v>16456</v>
+        <v>17581</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="74">
         <f t="shared" si="1"/>
-        <v>4206</v>
+        <v>4433</v>
       </c>
       <c r="Q6" s="36">
         <f t="shared" si="2"/>
-        <v>4433</v>
+        <v>4576</v>
       </c>
       <c r="R6" s="70">
         <f t="shared" ref="R6" si="4">K6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="27">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D7" s="27">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E7" s="27">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="F7" s="27">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G7" s="27">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="H7" s="27">
         <v>260</v>
@@ -7840,14 +7838,14 @@
         <v>260</v>
       </c>
       <c r="J7" s="27">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
       <c r="N7" s="42">
         <f>SUM(G7:J7)</f>
-        <v>1031</v>
+        <v>1041</v>
       </c>
       <c r="P7" s="53">
         <f t="shared" si="1"/>
@@ -7855,219 +7853,219 @@
       </c>
       <c r="Q7" s="20">
         <f t="shared" si="2"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R7" s="54">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>3.8461538461538464E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="58">
-        <f t="shared" ref="C8:D8" si="5">C5-C6-C7</f>
-        <v>2560</v>
+        <f t="shared" ref="C8" si="5">C5-C6-C7</f>
+        <v>2864</v>
       </c>
       <c r="D8" s="58">
-        <f t="shared" si="5"/>
-        <v>2864</v>
+        <f>D5-D6-D7</f>
+        <v>3419</v>
       </c>
       <c r="E8" s="58">
-        <f>E5-E6-E7</f>
-        <v>3419</v>
+        <f t="shared" ref="E8:H8" si="6">E5-E6-E7</f>
+        <v>3882</v>
       </c>
       <c r="F8" s="58">
-        <f t="shared" ref="F8:I8" si="6">F5-F6-F7</f>
-        <v>3882</v>
+        <f t="shared" si="6"/>
+        <v>3736</v>
       </c>
       <c r="G8" s="58">
         <f t="shared" si="6"/>
-        <v>3736</v>
+        <v>3059</v>
       </c>
       <c r="H8" s="58">
         <f t="shared" si="6"/>
-        <v>3059</v>
+        <v>4780</v>
       </c>
       <c r="I8" s="58">
-        <f t="shared" si="6"/>
-        <v>4780</v>
+        <f t="shared" ref="I8:J8" si="7">I5-I6-I7</f>
+        <v>5577</v>
       </c>
       <c r="J8" s="58">
-        <f t="shared" ref="J8" si="7">J5-J6-J7</f>
-        <v>5577</v>
+        <f t="shared" si="7"/>
+        <v>5416</v>
       </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
       <c r="N8" s="63">
         <f t="shared" si="0"/>
-        <v>17152</v>
+        <v>18832</v>
       </c>
       <c r="O8" s="7"/>
       <c r="P8" s="73">
         <f t="shared" si="1"/>
-        <v>4780</v>
+        <v>5577</v>
       </c>
       <c r="Q8" s="58">
         <f t="shared" si="2"/>
-        <v>5577</v>
+        <v>5416</v>
       </c>
       <c r="R8" s="69">
         <f t="shared" si="3"/>
-        <v>0.16673640167364018</v>
+        <v>-2.8868567330105791E-2</v>
       </c>
       <c r="S8" s="7"/>
     </row>
-    <row r="9" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="27">
-        <v>1525</v>
+        <v>1583</v>
       </c>
       <c r="D9" s="27">
-        <v>1583</v>
+        <v>1636</v>
       </c>
       <c r="E9" s="27">
-        <v>1636</v>
+        <v>1712</v>
       </c>
       <c r="F9" s="27">
-        <v>1712</v>
+        <v>1728</v>
       </c>
       <c r="G9" s="27">
-        <v>1728</v>
+        <v>1894</v>
       </c>
       <c r="H9" s="27">
-        <v>1894</v>
+        <v>2139</v>
       </c>
       <c r="I9" s="27">
-        <v>2139</v>
+        <v>2330</v>
       </c>
       <c r="J9" s="27">
-        <v>2330</v>
+        <v>2397</v>
       </c>
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
       <c r="M9" s="20"/>
       <c r="N9" s="42">
         <f t="shared" si="0"/>
-        <v>8091</v>
+        <v>8760</v>
       </c>
       <c r="P9" s="53">
         <f t="shared" si="1"/>
-        <v>2139</v>
+        <v>2330</v>
       </c>
       <c r="Q9" s="20">
         <f t="shared" si="2"/>
-        <v>2330</v>
+        <v>2397</v>
       </c>
       <c r="R9" s="54">
         <f t="shared" si="3"/>
-        <v>8.9294062646096309E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>2.8755364806866954E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="27">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="D10" s="27">
-        <v>650</v>
+        <v>707</v>
       </c>
       <c r="E10" s="27">
-        <v>707</v>
+        <v>781</v>
       </c>
       <c r="F10" s="27">
-        <v>781</v>
+        <v>886</v>
       </c>
       <c r="G10" s="27">
-        <v>886</v>
+        <v>991</v>
       </c>
       <c r="H10" s="27">
-        <v>991</v>
+        <v>1069</v>
       </c>
       <c r="I10" s="27">
-        <v>1069</v>
+        <v>1198</v>
       </c>
       <c r="J10" s="27">
-        <v>1198</v>
+        <v>1253</v>
       </c>
       <c r="K10" s="20"/>
       <c r="L10" s="20"/>
       <c r="M10" s="20"/>
       <c r="N10" s="42">
         <f t="shared" si="0"/>
-        <v>4144</v>
+        <v>4511</v>
       </c>
       <c r="P10" s="74">
         <f t="shared" si="1"/>
-        <v>1069</v>
+        <v>1198</v>
       </c>
       <c r="Q10" s="36">
         <f t="shared" si="2"/>
-        <v>1198</v>
+        <v>1253</v>
       </c>
       <c r="R10" s="70">
         <f t="shared" si="3"/>
-        <v>0.12067352666043031</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>4.5909849749582635E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="27">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="D11" s="27">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="E11" s="27">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="F11" s="27">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="G11" s="27">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="H11" s="27">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="I11" s="27">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="J11" s="27">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
       <c r="M11" s="20"/>
       <c r="N11" s="42">
         <f t="shared" si="0"/>
-        <v>1223</v>
+        <v>1197</v>
       </c>
       <c r="P11" s="74">
         <f t="shared" si="1"/>
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="Q11" s="36">
         <f t="shared" si="2"/>
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="R11" s="70">
         <f t="shared" si="3"/>
-        <v>-1.6556291390728478E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-2.3569023569023569E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C12" s="27">
         <v>0</v>
@@ -8076,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="27">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F12" s="27">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="G12" s="27">
         <v>0</v>
@@ -8113,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="8" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" s="8" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="12" t="s">
         <v>13</v>
       </c>
@@ -8161,15 +8159,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="27">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="D14" s="27">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E14" s="27">
         <v>0</v>
@@ -8209,114 +8207,114 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="20">
-        <f t="shared" ref="C15:I15" si="8">SUM(C9:C14)</f>
-        <v>2524</v>
+        <f t="shared" ref="C15:H15" si="8">SUM(C9:C14)</f>
+        <v>2595</v>
       </c>
       <c r="D15" s="20">
         <f t="shared" si="8"/>
-        <v>2595</v>
+        <v>2695</v>
       </c>
       <c r="E15" s="20">
         <f t="shared" si="8"/>
-        <v>2695</v>
+        <v>3011</v>
       </c>
       <c r="F15" s="20">
         <f t="shared" si="8"/>
-        <v>3011</v>
+        <v>2930</v>
       </c>
       <c r="G15" s="20">
         <f t="shared" si="8"/>
-        <v>2930</v>
+        <v>3193</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" si="8"/>
-        <v>3193</v>
+        <v>3510</v>
       </c>
       <c r="I15" s="20">
-        <f t="shared" si="8"/>
-        <v>3510</v>
+        <f t="shared" ref="I15:J15" si="9">SUM(I9:I14)</f>
+        <v>3825</v>
       </c>
       <c r="J15" s="20">
-        <f t="shared" ref="J15" si="9">SUM(J9:J14)</f>
-        <v>3825</v>
+        <f t="shared" si="9"/>
+        <v>3940</v>
       </c>
       <c r="K15" s="20"/>
       <c r="L15" s="20"/>
       <c r="M15" s="20"/>
       <c r="N15" s="42">
         <f t="shared" si="0"/>
-        <v>13458</v>
+        <v>14468</v>
       </c>
       <c r="P15" s="53">
         <f t="shared" si="1"/>
-        <v>3510</v>
+        <v>3825</v>
       </c>
       <c r="Q15" s="20">
         <f>J15</f>
-        <v>3825</v>
+        <v>3940</v>
       </c>
       <c r="R15" s="54">
         <f t="shared" si="3"/>
-        <v>8.9743589743589744E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>3.0065359477124184E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="55">
-        <v>36</v>
+        <v>269</v>
       </c>
       <c r="D16" s="55">
-        <v>269</v>
+        <v>724</v>
       </c>
       <c r="E16" s="55">
-        <v>724</v>
+        <v>871</v>
       </c>
       <c r="F16" s="55">
-        <v>871</v>
+        <v>806</v>
       </c>
       <c r="G16" s="55">
-        <v>806</v>
+        <v>-134</v>
       </c>
       <c r="H16" s="55">
-        <v>-134</v>
+        <v>1270</v>
       </c>
       <c r="I16" s="55">
-        <v>1270</v>
+        <v>1752</v>
       </c>
       <c r="J16" s="55">
-        <v>1752</v>
+        <v>1476</v>
       </c>
       <c r="K16" s="21"/>
       <c r="L16" s="21"/>
       <c r="M16" s="21"/>
       <c r="N16" s="63">
         <f t="shared" si="0"/>
-        <v>3694</v>
+        <v>4364</v>
       </c>
       <c r="O16" s="7"/>
       <c r="P16" s="73">
         <f t="shared" si="1"/>
-        <v>1270</v>
+        <v>1752</v>
       </c>
       <c r="Q16" s="58">
         <f t="shared" si="2"/>
-        <v>1752</v>
+        <v>1476</v>
       </c>
       <c r="R16" s="69">
         <f t="shared" si="3"/>
-        <v>0.37952755905511809</v>
+        <v>-0.15753424657534246</v>
       </c>
       <c r="S16" s="7"/>
     </row>
-    <row r="17" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="12" t="s">
         <v>52</v>
       </c>
@@ -8324,196 +8322,196 @@
         <v>-25</v>
       </c>
       <c r="D17" s="27">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="E17" s="27">
-        <v>-23</v>
+        <v>-19</v>
       </c>
       <c r="F17" s="27">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="G17" s="27">
-        <v>-20</v>
+        <v>-38</v>
       </c>
       <c r="H17" s="27">
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="I17" s="27">
+        <v>-36</v>
+      </c>
+      <c r="J17" s="27">
         <v>-37</v>
-      </c>
-      <c r="J17" s="27">
-        <v>-36</v>
       </c>
       <c r="K17" s="20"/>
       <c r="L17" s="20"/>
       <c r="M17" s="20"/>
       <c r="N17" s="42">
         <f t="shared" si="0"/>
-        <v>-131</v>
+        <v>-148</v>
       </c>
       <c r="P17" s="53">
         <f t="shared" si="1"/>
-        <v>-37</v>
+        <v>-36</v>
       </c>
       <c r="Q17" s="20">
         <f t="shared" si="2"/>
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="R17" s="54">
         <f t="shared" si="3"/>
-        <v>2.7027027027027029E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-2.7777777777777776E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="12" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="27">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="27">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E18" s="27">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F18" s="27">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G18" s="27">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="H18" s="27">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="I18" s="27">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="J18" s="27">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="K18" s="20"/>
       <c r="L18" s="20"/>
       <c r="M18" s="20"/>
       <c r="N18" s="42">
         <f t="shared" si="0"/>
-        <v>577</v>
+        <v>703</v>
       </c>
       <c r="P18" s="53">
         <f t="shared" si="1"/>
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Q18" s="20">
         <f t="shared" si="2"/>
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="R18" s="54">
         <f t="shared" si="3"/>
-        <v>3.3658536585365852</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-0.53910614525139666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="55">
-        <v>64</v>
+        <v>299</v>
       </c>
       <c r="D19" s="55">
-        <v>299</v>
+        <v>737</v>
       </c>
       <c r="E19" s="55">
-        <v>737</v>
+        <v>889</v>
       </c>
       <c r="F19" s="55">
-        <v>889</v>
+        <v>825</v>
       </c>
       <c r="G19" s="55">
-        <v>825</v>
+        <v>-74</v>
       </c>
       <c r="H19" s="55">
-        <v>-74</v>
+        <v>1315</v>
       </c>
       <c r="I19" s="55">
-        <v>1315</v>
+        <v>2074</v>
       </c>
       <c r="J19" s="55">
-        <v>2074</v>
+        <v>1604</v>
       </c>
       <c r="K19" s="21"/>
       <c r="L19" s="21"/>
       <c r="M19" s="21"/>
       <c r="N19" s="63">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>4919</v>
       </c>
       <c r="O19" s="7"/>
       <c r="P19" s="73">
         <f t="shared" si="1"/>
-        <v>1315</v>
+        <v>2074</v>
       </c>
       <c r="Q19" s="58">
         <f t="shared" si="2"/>
-        <v>2074</v>
+        <v>1604</v>
       </c>
       <c r="R19" s="69">
         <f t="shared" si="3"/>
-        <v>0.57718631178707225</v>
+        <v>-0.2266152362584378</v>
       </c>
       <c r="S19" s="7"/>
     </row>
-    <row r="20" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="27">
-        <v>52</v>
+        <v>-41</v>
       </c>
       <c r="D20" s="27">
-        <v>-41</v>
+        <v>27</v>
       </c>
       <c r="E20" s="27">
-        <v>27</v>
+        <v>-419</v>
       </c>
       <c r="F20" s="27">
-        <v>-419</v>
+        <v>-123</v>
       </c>
       <c r="G20" s="27">
-        <v>-123</v>
+        <v>834</v>
       </c>
       <c r="H20" s="27">
-        <v>834</v>
+        <v>-153</v>
       </c>
       <c r="I20" s="27">
-        <v>-153</v>
+        <v>-455</v>
       </c>
       <c r="J20" s="27">
-        <v>-455</v>
+        <v>-238</v>
       </c>
       <c r="K20" s="20"/>
       <c r="L20" s="20"/>
       <c r="M20" s="20"/>
       <c r="N20" s="42">
         <f t="shared" si="0"/>
-        <v>103</v>
+        <v>-12</v>
       </c>
       <c r="P20" s="53">
         <f t="shared" si="1"/>
-        <v>-153</v>
+        <v>-455</v>
       </c>
       <c r="Q20" s="20">
         <f t="shared" si="2"/>
-        <v>-455</v>
+        <v>-238</v>
       </c>
       <c r="R20" s="54">
         <f t="shared" si="3"/>
-        <v>-1.9738562091503269</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>0.47692307692307695</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C21" s="27">
         <v>7</v>
@@ -8522,95 +8520,95 @@
         <v>7</v>
       </c>
       <c r="E21" s="27">
+        <v>12</v>
+      </c>
+      <c r="F21" s="27">
         <v>7</v>
       </c>
-      <c r="F21" s="27">
-        <v>12</v>
-      </c>
       <c r="G21" s="27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21" s="27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21" s="27">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J21" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K21" s="20"/>
       <c r="L21" s="20"/>
       <c r="M21" s="20"/>
       <c r="N21" s="42">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="20">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R21" s="54">
         <f t="shared" si="3"/>
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="17" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="55">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="D22" s="55">
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="E22" s="55">
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="F22" s="55">
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="G22" s="55">
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="H22" s="55">
-        <v>768</v>
+        <v>1172</v>
       </c>
       <c r="I22" s="55">
-        <v>1172</v>
+        <v>1620</v>
       </c>
       <c r="J22" s="55">
-        <v>1620</v>
+        <v>1372</v>
       </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
       <c r="N22" s="63">
         <f t="shared" si="0"/>
-        <v>4269</v>
+        <v>4932</v>
       </c>
       <c r="O22" s="7"/>
       <c r="P22" s="73">
         <f t="shared" si="1"/>
-        <v>1172</v>
+        <v>1620</v>
       </c>
       <c r="Q22" s="58">
         <f t="shared" si="2"/>
-        <v>1620</v>
+        <v>1372</v>
       </c>
       <c r="R22" s="69">
         <f t="shared" si="3"/>
-        <v>0.38225255972696248</v>
+        <v>-0.15308641975308643</v>
       </c>
       <c r="S22" s="7"/>
     </row>
-    <row r="23" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="12" t="s">
         <v>17</v>
       </c>
@@ -8627,89 +8625,89 @@
         <v>0</v>
       </c>
       <c r="G23" s="27">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H23" s="27">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="I23" s="27">
-        <v>71</v>
+        <v>-109</v>
       </c>
       <c r="J23" s="27">
-        <v>-109</v>
+        <v>11</v>
       </c>
       <c r="K23" s="20"/>
       <c r="L23" s="20"/>
       <c r="M23" s="20"/>
       <c r="N23" s="42">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="P23" s="53">
         <f t="shared" si="1"/>
-        <v>71</v>
+        <v>-109</v>
       </c>
       <c r="Q23" s="20">
         <f t="shared" si="2"/>
-        <v>-109</v>
+        <v>11</v>
       </c>
       <c r="R23" s="54">
         <f t="shared" si="3"/>
-        <v>-2.535211267605634</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" s="37" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>1.1009174311926606</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="37" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" s="35">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="D24" s="35">
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="E24" s="35">
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="F24" s="35">
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="G24" s="35">
-        <v>709</v>
+        <v>872</v>
       </c>
       <c r="H24" s="35">
-        <v>872</v>
+        <v>1243</v>
       </c>
       <c r="I24" s="35">
-        <v>1243</v>
+        <v>1511</v>
       </c>
       <c r="J24" s="35">
-        <v>1511</v>
+        <v>1383</v>
       </c>
       <c r="K24" s="36"/>
       <c r="L24" s="36"/>
       <c r="M24" s="36"/>
       <c r="N24" s="43">
         <f t="shared" si="0"/>
-        <v>4335</v>
+        <v>5009</v>
       </c>
       <c r="O24" s="8"/>
       <c r="P24" s="75">
         <f t="shared" si="1"/>
-        <v>1243</v>
+        <v>1511</v>
       </c>
       <c r="Q24" s="76">
         <f t="shared" si="2"/>
-        <v>1511</v>
+        <v>1383</v>
       </c>
       <c r="R24" s="71">
         <f t="shared" si="3"/>
-        <v>0.21560740144810941</v>
+        <v>-8.471211118464593E-2</v>
       </c>
       <c r="S24" s="8"/>
     </row>
-    <row r="25" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="12" t="s">
         <v>19</v>
       </c>
@@ -8757,252 +8755,253 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="27">
-        <v>123</v>
+        <v>265</v>
       </c>
       <c r="D26" s="27">
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="E26" s="27">
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="F26" s="27">
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="G26" s="27">
-        <v>709</v>
+        <v>872</v>
       </c>
       <c r="H26" s="27">
-        <v>872</v>
+        <v>1243</v>
       </c>
       <c r="I26" s="27">
-        <v>1243</v>
+        <v>1511</v>
       </c>
       <c r="J26" s="27">
-        <v>1511</v>
+        <v>1383</v>
       </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
       <c r="M26" s="20"/>
       <c r="N26" s="42">
         <f t="shared" si="0"/>
-        <v>4335</v>
+        <v>5009</v>
       </c>
       <c r="P26" s="53">
         <f t="shared" si="1"/>
-        <v>1243</v>
+        <v>1511</v>
       </c>
       <c r="Q26" s="20">
         <f t="shared" si="2"/>
-        <v>1511</v>
+        <v>1383</v>
       </c>
       <c r="R26" s="54">
         <f t="shared" si="3"/>
-        <v>0.21560740144810941</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>-8.471211118464593E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="27">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D27" s="27">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="E27" s="27">
+        <v>1623</v>
+      </c>
+      <c r="F27" s="27">
         <v>1620</v>
       </c>
-      <c r="F27" s="27">
+      <c r="G27" s="27">
         <v>1623</v>
       </c>
-      <c r="G27" s="27">
-        <v>1620</v>
-      </c>
       <c r="H27" s="27">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="I27" s="27">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="J27" s="27">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
       <c r="M27" s="20"/>
       <c r="N27" s="42">
         <f>AVERAGE(G27:J27)</f>
-        <v>1624.75</v>
+        <v>1627.5</v>
       </c>
       <c r="P27" s="53">
         <f t="shared" si="1"/>
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="Q27" s="20">
         <f t="shared" si="2"/>
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="R27" s="54">
         <f t="shared" si="3"/>
-        <v>2.4600246002460025E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>6.1349693251533746E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="27">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="D28" s="27">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="E28" s="27">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="F28" s="27">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="G28" s="27">
-        <v>1626</v>
+        <v>1630</v>
       </c>
       <c r="H28" s="27">
-        <v>1630</v>
+        <v>1641</v>
       </c>
       <c r="I28" s="27">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="J28" s="27">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="K28" s="20"/>
       <c r="L28" s="20"/>
       <c r="M28" s="20"/>
       <c r="N28" s="42">
         <f>AVERAGE((G28:J28))</f>
-        <v>1636.5</v>
+        <v>1642.5</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="1"/>
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="Q28" s="20">
         <f t="shared" si="2"/>
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="R28" s="54">
         <f t="shared" si="3"/>
-        <v>4.8750761730652044E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>6.0642813826561554E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="12" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="31">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="D29" s="31">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="E29" s="31">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="F29" s="31">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="G29" s="31">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H29" s="31">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="I29" s="31">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="J29" s="31">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
       <c r="M29" s="25"/>
       <c r="N29" s="44">
         <f>N22/N27</f>
-        <v>2.6274811509462994</v>
+        <v>3.0304147465437787</v>
       </c>
       <c r="P29" s="77">
         <f t="shared" si="1"/>
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="Q29" s="78">
         <f t="shared" si="2"/>
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="R29" s="54">
         <f t="shared" si="3"/>
-        <v>0.22368421052631585</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" s="16" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>-8.6021505376344162E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" s="16" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C30" s="32">
-        <v>7.0000000000000007E-2</v>
+        <v>0.16</v>
       </c>
       <c r="D30" s="32">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="E30" s="32">
-        <v>0.47</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F30" s="32">
-        <v>0.28999999999999998</v>
+        <v>0.44</v>
       </c>
       <c r="G30" s="32">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H30" s="32">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="I30" s="32">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="J30" s="32">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
       <c r="N30" s="45">
         <f>N22/N28</f>
-        <v>2.6086159486709439</v>
+        <v>3.0027397260273974</v>
       </c>
       <c r="O30" s="1"/>
       <c r="P30" s="79">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="Q30" s="80">
         <f t="shared" si="2"/>
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="R30" s="72">
         <f t="shared" si="3"/>
-        <v>0.22666666666666671</v>
+        <v>-8.6956521739130502E-2</v>
       </c>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19" s="16" customFormat="1" ht="17" collapsed="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" s="16" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="6"/>
+      <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
@@ -9031,28 +9030,28 @@
         <v>27</v>
       </c>
       <c r="C33" s="27">
-        <v>4190</v>
+        <v>4113</v>
       </c>
       <c r="D33" s="27">
-        <v>4113</v>
+        <v>3897</v>
       </c>
       <c r="E33" s="27">
-        <v>3897</v>
+        <v>3787</v>
       </c>
       <c r="F33" s="27">
-        <v>3787</v>
+        <v>6049</v>
       </c>
       <c r="G33" s="27">
-        <v>6049</v>
+        <v>4442</v>
       </c>
       <c r="H33" s="27">
-        <v>4442</v>
+        <v>4808</v>
       </c>
       <c r="I33" s="27">
-        <v>4808</v>
+        <v>5539</v>
       </c>
       <c r="J33" s="27">
-        <v>5539</v>
+        <v>5585</v>
       </c>
       <c r="K33" s="20"/>
       <c r="L33" s="20"/>
@@ -9060,31 +9059,31 @@
     </row>
     <row r="34" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C34" s="27">
-        <v>1845</v>
+        <v>1227</v>
       </c>
       <c r="D34" s="27">
-        <v>1227</v>
+        <v>647</v>
       </c>
       <c r="E34" s="27">
-        <v>647</v>
+        <v>1345</v>
       </c>
       <c r="F34" s="27">
-        <v>1345</v>
+        <v>1261</v>
       </c>
       <c r="G34" s="27">
-        <v>1261</v>
+        <v>1425</v>
       </c>
       <c r="H34" s="27">
-        <v>1425</v>
+        <v>2435</v>
       </c>
       <c r="I34" s="27">
-        <v>2435</v>
+        <v>5013</v>
       </c>
       <c r="J34" s="27">
-        <v>5013</v>
+        <v>6762</v>
       </c>
       <c r="K34" s="20"/>
       <c r="L34" s="20"/>
@@ -9095,28 +9094,28 @@
         <v>28</v>
       </c>
       <c r="C35" s="27">
-        <v>5038</v>
+        <v>5749</v>
       </c>
       <c r="D35" s="27">
-        <v>5749</v>
+        <v>7241</v>
       </c>
       <c r="E35" s="27">
-        <v>7241</v>
+        <v>6192</v>
       </c>
       <c r="F35" s="27">
-        <v>6192</v>
+        <v>5443</v>
       </c>
       <c r="G35" s="27">
-        <v>5443</v>
+        <v>5115</v>
       </c>
       <c r="H35" s="27">
-        <v>5115</v>
+        <v>6201</v>
       </c>
       <c r="I35" s="27">
-        <v>6201</v>
+        <v>6315</v>
       </c>
       <c r="J35" s="27">
-        <v>6315</v>
+        <v>6035</v>
       </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20"/>
@@ -9127,28 +9126,28 @@
         <v>29</v>
       </c>
       <c r="C36" s="27">
-        <v>4652</v>
+        <v>4991</v>
       </c>
       <c r="D36" s="27">
-        <v>4991</v>
+        <v>5374</v>
       </c>
       <c r="E36" s="27">
-        <v>5374</v>
+        <v>5734</v>
       </c>
       <c r="F36" s="27">
-        <v>5734</v>
+        <v>6416</v>
       </c>
       <c r="G36" s="27">
-        <v>6416</v>
+        <v>6677</v>
       </c>
       <c r="H36" s="27">
-        <v>6677</v>
+        <v>7313</v>
       </c>
       <c r="I36" s="27">
-        <v>7313</v>
+        <v>7920</v>
       </c>
       <c r="J36" s="27">
-        <v>7920</v>
+        <v>8045</v>
       </c>
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
@@ -9156,16 +9155,16 @@
     </row>
     <row r="37" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C37" s="27">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D37" s="27">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E37" s="27">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F37" s="27">
         <v>0</v>
@@ -9188,7 +9187,7 @@
     </row>
     <row r="38" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" s="27">
         <v>0</v>
@@ -9235,13 +9234,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="27">
-        <v>0</v>
+        <v>4326</v>
       </c>
       <c r="H39" s="27">
-        <v>4326</v>
+        <v>3990</v>
       </c>
       <c r="I39" s="27">
-        <v>3990</v>
+        <v>0</v>
       </c>
       <c r="J39" s="27">
         <v>0</v>
@@ -9255,28 +9254,28 @@
         <v>30</v>
       </c>
       <c r="C40" s="27">
-        <v>1328</v>
+        <v>1361</v>
       </c>
       <c r="D40" s="27">
-        <v>1361</v>
+        <v>1547</v>
       </c>
       <c r="E40" s="27">
-        <v>1547</v>
+        <v>1991</v>
       </c>
       <c r="F40" s="27">
-        <v>1991</v>
+        <v>2426</v>
       </c>
       <c r="G40" s="27">
-        <v>2426</v>
+        <v>2534</v>
       </c>
       <c r="H40" s="27">
-        <v>2534</v>
+        <v>2253</v>
       </c>
       <c r="I40" s="27">
-        <v>2253</v>
+        <v>2160</v>
       </c>
       <c r="J40" s="27">
-        <v>2160</v>
+        <v>2201</v>
       </c>
       <c r="K40" s="20"/>
       <c r="L40" s="20"/>
@@ -9287,28 +9286,28 @@
         <v>31</v>
       </c>
       <c r="C41" s="59">
-        <v>17084</v>
+        <v>17465</v>
       </c>
       <c r="D41" s="59">
-        <v>17465</v>
+        <v>18735</v>
       </c>
       <c r="E41" s="59">
-        <v>18735</v>
+        <v>19049</v>
       </c>
       <c r="F41" s="59">
-        <v>19049</v>
+        <v>21595</v>
       </c>
       <c r="G41" s="59">
-        <v>21595</v>
+        <v>14519</v>
       </c>
       <c r="H41" s="59">
-        <v>14519</v>
+        <v>27000</v>
       </c>
       <c r="I41" s="59">
-        <v>27000</v>
+        <v>26947</v>
       </c>
       <c r="J41" s="59">
-        <v>26947</v>
+        <v>28628</v>
       </c>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
@@ -9319,28 +9318,28 @@
         <v>33</v>
       </c>
       <c r="C42" s="27">
-        <v>1624</v>
+        <v>1666</v>
       </c>
       <c r="D42" s="27">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="E42" s="27">
-        <v>1669</v>
+        <v>1802</v>
       </c>
       <c r="F42" s="27">
-        <v>1802</v>
+        <v>1921</v>
       </c>
       <c r="G42" s="27">
-        <v>1921</v>
+        <v>2128</v>
       </c>
       <c r="H42" s="27">
-        <v>2128</v>
+        <v>2205</v>
       </c>
       <c r="I42" s="27">
-        <v>2205</v>
+        <v>2312</v>
       </c>
       <c r="J42" s="27">
-        <v>2312</v>
+        <v>2723</v>
       </c>
       <c r="K42" s="20"/>
       <c r="L42" s="20"/>
@@ -9348,16 +9347,16 @@
     </row>
     <row r="43" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C43" s="27">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D43" s="27">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="E43" s="27">
-        <v>647</v>
+        <v>0</v>
       </c>
       <c r="F43" s="27">
         <v>0</v>
@@ -9386,7 +9385,7 @@
         <v>24262</v>
       </c>
       <c r="D44" s="27">
-        <v>24262</v>
+        <v>24839</v>
       </c>
       <c r="E44" s="27">
         <v>24839</v>
@@ -9395,16 +9394,16 @@
         <v>24839</v>
       </c>
       <c r="G44" s="27">
-        <v>24839</v>
+        <v>25083</v>
       </c>
       <c r="H44" s="27">
         <v>25083</v>
       </c>
       <c r="I44" s="27">
-        <v>25083</v>
+        <v>25126</v>
       </c>
       <c r="J44" s="27">
-        <v>25126</v>
+        <v>25344</v>
       </c>
       <c r="K44" s="20"/>
       <c r="L44" s="20"/>
@@ -9412,31 +9411,31 @@
     </row>
     <row r="45" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C45" s="27">
-        <v>20741</v>
+        <v>20138</v>
       </c>
       <c r="D45" s="27">
-        <v>20138</v>
+        <v>19572</v>
       </c>
       <c r="E45" s="27">
-        <v>19572</v>
+        <v>18930</v>
       </c>
       <c r="F45" s="27">
-        <v>18930</v>
+        <v>18363</v>
       </c>
       <c r="G45" s="27">
-        <v>18363</v>
+        <v>17812</v>
       </c>
       <c r="H45" s="27">
-        <v>17812</v>
+        <v>17250</v>
       </c>
       <c r="I45" s="27">
-        <v>17250</v>
+        <v>16705</v>
       </c>
       <c r="J45" s="27">
-        <v>16705</v>
+        <v>16154</v>
       </c>
       <c r="K45" s="20"/>
       <c r="L45" s="20"/>
@@ -9444,16 +9443,16 @@
     </row>
     <row r="46" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C46" s="27">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D46" s="27">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E46" s="27">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="F46" s="27">
         <v>0</v>
@@ -9479,28 +9478,28 @@
         <v>32</v>
       </c>
       <c r="C47" s="27">
-        <v>433</v>
+        <v>617</v>
       </c>
       <c r="D47" s="27">
-        <v>617</v>
+        <v>1183</v>
       </c>
       <c r="E47" s="27">
-        <v>1183</v>
+        <v>688</v>
       </c>
       <c r="F47" s="27">
-        <v>688</v>
+        <v>845</v>
       </c>
       <c r="G47" s="27">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="H47" s="27">
-        <v>860</v>
+        <v>633</v>
       </c>
       <c r="I47" s="27">
-        <v>633</v>
+        <v>384</v>
       </c>
       <c r="J47" s="27">
-        <v>384</v>
+        <v>476</v>
       </c>
       <c r="K47" s="20"/>
       <c r="L47" s="20"/>
@@ -9511,28 +9510,28 @@
         <v>35</v>
       </c>
       <c r="C48" s="27">
-        <v>3013</v>
+        <v>2990</v>
       </c>
       <c r="D48" s="27">
-        <v>2990</v>
+        <v>2854</v>
       </c>
       <c r="E48" s="27">
-        <v>2854</v>
+        <v>3918</v>
       </c>
       <c r="F48" s="27">
-        <v>3918</v>
+        <v>3987</v>
       </c>
       <c r="G48" s="27">
-        <v>3987</v>
+        <v>4418</v>
       </c>
       <c r="H48" s="27">
-        <v>4418</v>
+        <v>4720</v>
       </c>
       <c r="I48" s="27">
-        <v>4720</v>
+        <v>5452</v>
       </c>
       <c r="J48" s="27">
-        <v>5452</v>
+        <v>6317</v>
       </c>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
@@ -9543,36 +9542,36 @@
         <v>36</v>
       </c>
       <c r="C49" s="60">
-        <f>SUM(C42:C48)</f>
-        <v>50811</v>
+        <f t="shared" ref="C49:H49" si="10">SUM(C42:C48)</f>
+        <v>50421</v>
       </c>
       <c r="D49" s="60">
-        <f t="shared" ref="D49:I49" si="10">SUM(D42:D48)</f>
-        <v>50421</v>
+        <f t="shared" si="10"/>
+        <v>50901</v>
       </c>
       <c r="E49" s="60">
         <f t="shared" si="10"/>
-        <v>50901</v>
+        <v>50177</v>
       </c>
       <c r="F49" s="60">
         <f t="shared" si="10"/>
-        <v>50177</v>
+        <v>49955</v>
       </c>
       <c r="G49" s="60">
         <f t="shared" si="10"/>
-        <v>49955</v>
+        <v>50301</v>
       </c>
       <c r="H49" s="60">
         <f t="shared" si="10"/>
-        <v>50301</v>
+        <v>49891</v>
       </c>
       <c r="I49" s="60">
-        <f t="shared" si="10"/>
-        <v>49891</v>
+        <f t="shared" ref="I49:J49" si="11">SUM(I42:I48)</f>
+        <v>49979</v>
       </c>
       <c r="J49" s="60">
-        <f t="shared" ref="J49" si="11">SUM(J42:J48)</f>
-        <v>49979</v>
+        <f t="shared" si="11"/>
+        <v>51014</v>
       </c>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
@@ -9584,28 +9583,28 @@
         <v>37</v>
       </c>
       <c r="C50" s="55">
-        <v>67895</v>
+        <v>67886</v>
       </c>
       <c r="D50" s="55">
-        <v>67886</v>
+        <v>69636</v>
       </c>
       <c r="E50" s="55">
-        <v>69636</v>
+        <v>69226</v>
       </c>
       <c r="F50" s="55">
-        <v>69226</v>
+        <v>71550</v>
       </c>
       <c r="G50" s="55">
-        <v>71550</v>
+        <v>74820</v>
       </c>
       <c r="H50" s="55">
-        <v>74820</v>
+        <v>76891</v>
       </c>
       <c r="I50" s="55">
-        <v>76891</v>
+        <v>76926</v>
       </c>
       <c r="J50" s="55">
-        <v>76926</v>
+        <v>79642</v>
       </c>
       <c r="K50" s="21"/>
       <c r="L50" s="21"/>
@@ -9618,7 +9617,7 @@
         <v>39</v>
       </c>
       <c r="C51" s="27">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="D51" s="27">
         <v>0</v>
@@ -9627,16 +9626,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="27">
-        <v>0</v>
+        <v>947</v>
       </c>
       <c r="G51" s="27">
-        <v>947</v>
+        <v>0</v>
       </c>
       <c r="H51" s="27">
-        <v>0</v>
+        <v>873</v>
       </c>
       <c r="I51" s="27">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="J51" s="27">
         <v>874</v>
@@ -9650,28 +9649,28 @@
         <v>38</v>
       </c>
       <c r="C52" s="27">
-        <v>1418</v>
+        <v>1699</v>
       </c>
       <c r="D52" s="27">
-        <v>1699</v>
+        <v>2530</v>
       </c>
       <c r="E52" s="27">
-        <v>2530</v>
+        <v>2466</v>
       </c>
       <c r="F52" s="27">
-        <v>2466</v>
+        <v>2206</v>
       </c>
       <c r="G52" s="27">
-        <v>2206</v>
+        <v>3080</v>
       </c>
       <c r="H52" s="27">
-        <v>3080</v>
+        <v>3483</v>
       </c>
       <c r="I52" s="27">
-        <v>3483</v>
+        <v>2929</v>
       </c>
       <c r="J52" s="27">
-        <v>2929</v>
+        <v>2997</v>
       </c>
       <c r="K52" s="20"/>
       <c r="L52" s="20"/>
@@ -9679,16 +9678,16 @@
     </row>
     <row r="53" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B53" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C53" s="27">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="D53" s="27">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="E53" s="27">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="F53" s="27">
         <v>0</v>
@@ -9711,31 +9710,31 @@
     </row>
     <row r="54" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B54" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C54" s="27">
-        <v>3444</v>
+        <v>3629</v>
       </c>
       <c r="D54" s="27">
-        <v>3629</v>
+        <v>4120</v>
       </c>
       <c r="E54" s="27">
-        <v>4120</v>
+        <v>4260</v>
       </c>
       <c r="F54" s="27">
-        <v>4260</v>
+        <v>3876</v>
       </c>
       <c r="G54" s="27">
-        <v>3876</v>
+        <v>4479</v>
       </c>
       <c r="H54" s="27">
-        <v>4479</v>
+        <v>5112</v>
       </c>
       <c r="I54" s="27">
-        <v>5112</v>
+        <v>5250</v>
       </c>
       <c r="J54" s="27">
-        <v>5250</v>
+        <v>5785</v>
       </c>
       <c r="K54" s="20"/>
       <c r="L54" s="20"/>
@@ -9758,13 +9757,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="27">
-        <v>0</v>
+        <v>1968</v>
       </c>
       <c r="H55" s="27">
-        <v>1968</v>
+        <v>1908</v>
       </c>
       <c r="I55" s="27">
-        <v>1908</v>
+        <v>0</v>
       </c>
       <c r="J55" s="27">
         <v>0</v>
@@ -9778,28 +9777,28 @@
         <v>40</v>
       </c>
       <c r="C56" s="27">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="D56" s="27">
-        <v>447</v>
+        <v>389</v>
       </c>
       <c r="E56" s="27">
-        <v>389</v>
+        <v>555</v>
       </c>
       <c r="F56" s="27">
-        <v>555</v>
+        <v>674</v>
       </c>
       <c r="G56" s="27">
-        <v>674</v>
+        <v>316</v>
       </c>
       <c r="H56" s="27">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="I56" s="27">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="J56" s="27">
-        <v>402</v>
+        <v>850</v>
       </c>
       <c r="K56" s="20"/>
       <c r="L56" s="20"/>
@@ -9807,7 +9806,7 @@
     </row>
     <row r="57" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B57" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C57" s="27">
         <v>0</v>
@@ -9842,28 +9841,28 @@
         <v>45</v>
       </c>
       <c r="C58" s="59">
-        <v>6474</v>
+        <v>6195</v>
       </c>
       <c r="D58" s="59">
-        <v>6195</v>
+        <v>7500</v>
       </c>
       <c r="E58" s="59">
-        <v>7500</v>
+        <v>7281</v>
       </c>
       <c r="F58" s="59">
-        <v>7281</v>
+        <v>7703</v>
       </c>
       <c r="G58" s="59">
-        <v>7703</v>
+        <v>9843</v>
       </c>
       <c r="H58" s="59">
-        <v>9843</v>
+        <v>11700</v>
       </c>
       <c r="I58" s="59">
-        <v>11700</v>
+        <v>9455</v>
       </c>
       <c r="J58" s="59">
-        <v>9455</v>
+        <v>10506</v>
       </c>
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
@@ -9874,28 +9873,28 @@
         <v>41</v>
       </c>
       <c r="C59" s="27">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D59" s="27">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="E59" s="27">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="F59" s="27">
-        <v>1721</v>
+        <v>3217</v>
       </c>
       <c r="G59" s="27">
-        <v>3217</v>
+        <v>3218</v>
       </c>
       <c r="H59" s="27">
-        <v>3218</v>
+        <v>2347</v>
       </c>
       <c r="I59" s="27">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="J59" s="27">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="K59" s="20"/>
       <c r="L59" s="20"/>
@@ -9903,31 +9902,31 @@
     </row>
     <row r="60" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B60" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C60" s="27">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D60" s="27">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E60" s="27">
-        <v>518</v>
+        <v>491</v>
       </c>
       <c r="F60" s="27">
-        <v>491</v>
+        <v>567</v>
       </c>
       <c r="G60" s="27">
-        <v>567</v>
+        <v>668</v>
       </c>
       <c r="H60" s="27">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="I60" s="27">
-        <v>650</v>
+        <v>625</v>
       </c>
       <c r="J60" s="27">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="K60" s="20"/>
       <c r="L60" s="20"/>
@@ -9935,31 +9934,31 @@
     </row>
     <row r="61" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B61" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C61" s="27">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="D61" s="27">
-        <v>1192</v>
+        <v>1162</v>
       </c>
       <c r="E61" s="27">
-        <v>1162</v>
+        <v>349</v>
       </c>
       <c r="F61" s="27">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G61" s="27">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H61" s="27">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="I61" s="27">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="J61" s="27">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K61" s="20"/>
       <c r="L61" s="20"/>
@@ -9970,28 +9969,28 @@
         <v>42</v>
       </c>
       <c r="C62" s="27">
-        <v>1776</v>
+        <v>1716</v>
       </c>
       <c r="D62" s="27">
-        <v>1716</v>
+        <v>1751</v>
       </c>
       <c r="E62" s="27">
-        <v>1751</v>
+        <v>1816</v>
       </c>
       <c r="F62" s="27">
-        <v>1816</v>
+        <v>1839</v>
       </c>
       <c r="G62" s="27">
-        <v>1839</v>
+        <v>1085</v>
       </c>
       <c r="H62" s="27">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="I62" s="27">
-        <v>1078</v>
+        <v>1186</v>
       </c>
       <c r="J62" s="27">
-        <v>1186</v>
+        <v>1370</v>
       </c>
       <c r="K62" s="20"/>
       <c r="L62" s="20"/>
@@ -10002,36 +10001,36 @@
         <v>43</v>
       </c>
       <c r="C63" s="60">
-        <f t="shared" ref="C63:I63" si="12">SUM(C59:C62)</f>
-        <v>5223</v>
+        <f t="shared" ref="C63:H63" si="12">SUM(C59:C62)</f>
+        <v>5153</v>
       </c>
       <c r="D63" s="60">
         <f t="shared" si="12"/>
-        <v>5153</v>
+        <v>5151</v>
       </c>
       <c r="E63" s="60">
         <f t="shared" si="12"/>
-        <v>5151</v>
+        <v>4377</v>
       </c>
       <c r="F63" s="60">
         <f t="shared" si="12"/>
-        <v>4377</v>
+        <v>5966</v>
       </c>
       <c r="G63" s="60">
         <f t="shared" si="12"/>
-        <v>5966</v>
+        <v>5312</v>
       </c>
       <c r="H63" s="60">
         <f t="shared" si="12"/>
-        <v>5312</v>
+        <v>4401</v>
       </c>
       <c r="I63" s="60">
-        <f t="shared" si="12"/>
-        <v>4401</v>
+        <f t="shared" ref="I63:J63" si="13">SUM(I59:I62)</f>
+        <v>4472</v>
       </c>
       <c r="J63" s="60">
-        <f t="shared" ref="J63" si="13">SUM(J59:J62)</f>
-        <v>4472</v>
+        <f t="shared" si="13"/>
+        <v>4674</v>
       </c>
       <c r="K63" s="21"/>
       <c r="L63" s="21"/>
@@ -10043,36 +10042,36 @@
         <v>44</v>
       </c>
       <c r="C64" s="58">
-        <f t="shared" ref="C64:I64" si="14">C58+C63</f>
-        <v>11697</v>
+        <f t="shared" ref="C64:H64" si="14">C58+C63</f>
+        <v>11348</v>
       </c>
       <c r="D64" s="58">
         <f t="shared" si="14"/>
-        <v>11348</v>
+        <v>12651</v>
       </c>
       <c r="E64" s="58">
         <f t="shared" si="14"/>
-        <v>12651</v>
+        <v>11658</v>
       </c>
       <c r="F64" s="58">
         <f t="shared" si="14"/>
-        <v>11658</v>
+        <v>13669</v>
       </c>
       <c r="G64" s="58">
         <f t="shared" si="14"/>
-        <v>13669</v>
+        <v>15155</v>
       </c>
       <c r="H64" s="58">
         <f t="shared" si="14"/>
-        <v>15155</v>
+        <v>16101</v>
       </c>
       <c r="I64" s="58">
-        <f t="shared" si="14"/>
-        <v>16101</v>
+        <f t="shared" ref="I64:J64" si="15">I58+I63</f>
+        <v>13927</v>
       </c>
       <c r="J64" s="58">
-        <f t="shared" ref="J64" si="15">J58+J63</f>
-        <v>13927</v>
+        <f t="shared" si="15"/>
+        <v>15180</v>
       </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -10114,31 +10113,31 @@
     </row>
     <row r="66" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B66" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C66" s="27">
-        <v>60053</v>
+        <v>60542</v>
       </c>
       <c r="D66" s="27">
-        <v>60542</v>
+        <v>60896</v>
       </c>
       <c r="E66" s="27">
-        <v>60896</v>
+        <v>61362</v>
       </c>
       <c r="F66" s="27">
-        <v>61362</v>
+        <v>61730</v>
       </c>
       <c r="G66" s="27">
-        <v>61730</v>
+        <v>62228</v>
       </c>
       <c r="H66" s="27">
-        <v>62228</v>
+        <v>62657</v>
       </c>
       <c r="I66" s="27">
-        <v>62657</v>
+        <v>63365</v>
       </c>
       <c r="J66" s="27">
-        <v>63365</v>
+        <v>63856</v>
       </c>
       <c r="K66" s="20"/>
       <c r="L66" s="20"/>
@@ -10146,31 +10145,31 @@
     </row>
     <row r="67" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B67" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C67" s="27">
-        <v>-4690</v>
+        <v>-5103</v>
       </c>
       <c r="D67" s="27">
-        <v>-5103</v>
+        <v>-5812</v>
       </c>
       <c r="E67" s="27">
-        <v>-5812</v>
+        <v>-6106</v>
       </c>
       <c r="F67" s="27">
-        <v>-6106</v>
+        <v>-6899</v>
       </c>
       <c r="G67" s="27">
-        <v>-6899</v>
+        <v>-6535</v>
       </c>
       <c r="H67" s="27">
-        <v>-6535</v>
+        <v>-7059</v>
       </c>
       <c r="I67" s="27">
-        <v>-7059</v>
+        <v>-7079</v>
       </c>
       <c r="J67" s="27">
-        <v>-7079</v>
+        <v>-7421</v>
       </c>
       <c r="K67" s="20"/>
       <c r="L67" s="20"/>
@@ -10181,28 +10180,28 @@
         <v>47</v>
       </c>
       <c r="C68" s="27">
-        <v>846</v>
+        <v>1111</v>
       </c>
       <c r="D68" s="27">
-        <v>1111</v>
+        <v>1882</v>
       </c>
       <c r="E68" s="27">
-        <v>1882</v>
+        <v>2364</v>
       </c>
       <c r="F68" s="27">
-        <v>2364</v>
+        <v>3073</v>
       </c>
       <c r="G68" s="27">
-        <v>3073</v>
+        <v>3945</v>
       </c>
       <c r="H68" s="27">
-        <v>3945</v>
+        <v>5188</v>
       </c>
       <c r="I68" s="27">
-        <v>5188</v>
+        <v>6699</v>
       </c>
       <c r="J68" s="27">
-        <v>6699</v>
+        <v>8082</v>
       </c>
       <c r="K68" s="20"/>
       <c r="L68" s="20"/>
@@ -10213,28 +10212,28 @@
         <v>48</v>
       </c>
       <c r="C69" s="27">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="D69" s="27">
-        <v>-29</v>
+        <v>2</v>
       </c>
       <c r="E69" s="27">
-        <v>2</v>
+        <v>-69</v>
       </c>
       <c r="F69" s="27">
-        <v>-69</v>
+        <v>-40</v>
       </c>
       <c r="G69" s="27">
-        <v>-40</v>
+        <v>10</v>
       </c>
       <c r="H69" s="27">
-        <v>10</v>
+        <v>-13</v>
       </c>
       <c r="I69" s="27">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="J69" s="27">
-        <v>-3</v>
+        <v>-72</v>
       </c>
       <c r="K69" s="20"/>
       <c r="L69" s="20"/>
@@ -10245,28 +10244,28 @@
         <v>49</v>
       </c>
       <c r="C70" s="59">
-        <v>56198</v>
+        <v>56538</v>
       </c>
       <c r="D70" s="59">
-        <v>56538</v>
+        <v>56985</v>
       </c>
       <c r="E70" s="59">
-        <v>56985</v>
+        <v>57568</v>
       </c>
       <c r="F70" s="59">
-        <v>57568</v>
+        <v>57881</v>
       </c>
       <c r="G70" s="59">
-        <v>57881</v>
+        <v>59665</v>
       </c>
       <c r="H70" s="59">
-        <v>59665</v>
+        <v>60790</v>
       </c>
       <c r="I70" s="59">
-        <v>60790</v>
+        <v>62999</v>
       </c>
       <c r="J70" s="59">
-        <v>62999</v>
+        <v>64462</v>
       </c>
       <c r="K70" s="21"/>
       <c r="L70" s="21"/>
@@ -10309,28 +10308,28 @@
         <v>50</v>
       </c>
       <c r="C72" s="27">
-        <v>56198</v>
+        <v>56538</v>
       </c>
       <c r="D72" s="27">
-        <v>56538</v>
+        <v>56985</v>
       </c>
       <c r="E72" s="27">
-        <v>56985</v>
+        <v>57568</v>
       </c>
       <c r="F72" s="27">
-        <v>57568</v>
+        <v>57881</v>
       </c>
       <c r="G72" s="27">
-        <v>57881</v>
+        <v>59665</v>
       </c>
       <c r="H72" s="27">
-        <v>59665</v>
+        <v>60790</v>
       </c>
       <c r="I72" s="27">
-        <v>60790</v>
+        <v>62999</v>
       </c>
       <c r="J72" s="27">
-        <v>62999</v>
+        <v>64462</v>
       </c>
       <c r="K72" s="20"/>
       <c r="L72" s="20"/>
@@ -10342,28 +10341,28 @@
         <v>51</v>
       </c>
       <c r="C73" s="62">
-        <v>67895</v>
+        <v>67886</v>
       </c>
       <c r="D73" s="62">
-        <v>67886</v>
+        <v>69636</v>
       </c>
       <c r="E73" s="62">
-        <v>69636</v>
+        <v>69226</v>
       </c>
       <c r="F73" s="62">
-        <v>69226</v>
+        <v>71550</v>
       </c>
       <c r="G73" s="62">
-        <v>71550</v>
+        <v>74820</v>
       </c>
       <c r="H73" s="62">
-        <v>74820</v>
+        <v>76891</v>
       </c>
       <c r="I73" s="62">
-        <v>76891</v>
+        <v>76926</v>
       </c>
       <c r="J73" s="62">
-        <v>76926</v>
+        <v>79642</v>
       </c>
       <c r="K73" s="21"/>
       <c r="L73" s="21"/>
@@ -10385,49 +10384,49 @@
       <c r="O75" s="4"/>
       <c r="S75" s="4"/>
     </row>
-    <row r="76" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B76" s="9" t="s">
         <v>18</v>
       </c>
       <c r="C76" s="20">
-        <f t="shared" ref="C76:I76" si="16">C24</f>
-        <v>123</v>
+        <f t="shared" ref="C76:H76" si="16">C24</f>
+        <v>265</v>
       </c>
       <c r="D76" s="20">
         <f t="shared" si="16"/>
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="E76" s="20">
         <f t="shared" si="16"/>
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="F76" s="20">
         <f t="shared" si="16"/>
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="G76" s="20">
         <f t="shared" si="16"/>
-        <v>709</v>
+        <v>872</v>
       </c>
       <c r="H76" s="20">
         <f t="shared" si="16"/>
-        <v>872</v>
+        <v>1243</v>
       </c>
       <c r="I76" s="20">
-        <f t="shared" si="16"/>
-        <v>1243</v>
+        <f t="shared" ref="I76:J76" si="17">I24</f>
+        <v>1511</v>
       </c>
       <c r="J76" s="20">
-        <f t="shared" ref="J76" si="17">J24</f>
-        <v>1511</v>
+        <f t="shared" si="17"/>
+        <v>1383</v>
       </c>
       <c r="K76" s="20"/>
       <c r="L76" s="20"/>
       <c r="M76" s="20"/>
     </row>
-    <row r="77" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B77" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C77" s="92">
         <v>0</v>
@@ -10441,153 +10440,153 @@
       <c r="F77" s="92">
         <v>0</v>
       </c>
-      <c r="G77" s="92">
-        <v>0</v>
+      <c r="G77" s="20">
+        <v>-104</v>
       </c>
       <c r="H77" s="20">
-        <v>-104</v>
-      </c>
-      <c r="I77" s="20">
         <v>-71</v>
       </c>
+      <c r="I77" s="27">
+        <v>109</v>
+      </c>
       <c r="J77" s="27">
-        <v>109</v>
+        <v>-11</v>
       </c>
       <c r="K77" s="20"/>
       <c r="L77" s="20"/>
       <c r="M77" s="20"/>
     </row>
-    <row r="78" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B78" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C78" s="27">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D78" s="27">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E78" s="27">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F78" s="27">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G78" s="27">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="H78" s="27">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I78" s="27">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J78" s="27">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="K78" s="27"/>
       <c r="L78" s="27"/>
       <c r="M78" s="20"/>
     </row>
-    <row r="79" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B79" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C79" s="27">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="D79" s="27">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="E79" s="27">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F79" s="27">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="G79" s="27">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H79" s="27">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="I79" s="27">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="J79" s="27">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="K79" s="27"/>
       <c r="L79" s="27"/>
       <c r="M79" s="20"/>
     </row>
-    <row r="80" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B80" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C80" s="27">
-        <v>-66</v>
+        <v>-190</v>
       </c>
       <c r="D80" s="27">
-        <v>-190</v>
+        <v>-607</v>
       </c>
       <c r="E80" s="27">
-        <v>-607</v>
+        <v>-300</v>
       </c>
       <c r="F80" s="27">
-        <v>-300</v>
+        <v>-167</v>
       </c>
       <c r="G80" s="27">
-        <v>-167</v>
+        <v>-33</v>
       </c>
       <c r="H80" s="27">
-        <v>-33</v>
+        <v>218</v>
       </c>
       <c r="I80" s="27">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J80" s="27">
-        <v>230</v>
+        <v>-79</v>
       </c>
       <c r="K80" s="27"/>
       <c r="L80" s="27"/>
       <c r="M80" s="20"/>
     </row>
-    <row r="81" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B81" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="27">
-        <v>371</v>
+        <v>346</v>
       </c>
       <c r="D81" s="27">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E81" s="27">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="F81" s="27">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="G81" s="27">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H81" s="27">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="I81" s="27">
-        <v>419</v>
+        <v>486</v>
       </c>
       <c r="J81" s="27">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K81" s="27"/>
       <c r="L81" s="27"/>
       <c r="M81" s="20"/>
     </row>
-    <row r="82" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B82" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C82" s="27">
         <v>0</v>
@@ -10608,18 +10607,18 @@
         <v>0</v>
       </c>
       <c r="I82" s="27">
-        <v>0</v>
+        <v>-280</v>
       </c>
       <c r="J82" s="27">
-        <v>-280</v>
+        <v>-66</v>
       </c>
       <c r="K82" s="27"/>
       <c r="L82" s="27"/>
       <c r="M82" s="20"/>
     </row>
-    <row r="83" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B83" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C83" s="27">
         <v>0</v>
@@ -10628,10 +10627,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="27">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F83" s="27">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G83" s="27">
         <v>0</v>
@@ -10649,9 +10648,9 @@
       <c r="L83" s="27"/>
       <c r="M83" s="20"/>
     </row>
-    <row r="84" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B84" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C84" s="27">
         <v>0</v>
@@ -10681,9 +10680,9 @@
       <c r="L84" s="27"/>
       <c r="M84" s="20"/>
     </row>
-    <row r="85" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B85" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C85" s="27">
         <v>0</v>
@@ -10698,10 +10697,10 @@
         <v>0</v>
       </c>
       <c r="G85" s="27">
-        <v>0</v>
+        <v>-853</v>
       </c>
       <c r="H85" s="27">
-        <v>-853</v>
+        <v>0</v>
       </c>
       <c r="I85" s="27">
         <v>0</v>
@@ -10713,12 +10712,12 @@
       <c r="L85" s="27"/>
       <c r="M85" s="20"/>
     </row>
-    <row r="86" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B86" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C86" s="27">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D86" s="27">
         <v>0</v>
@@ -10733,10 +10732,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="27">
-        <v>0</v>
+        <v>-67</v>
       </c>
       <c r="I86" s="27">
-        <v>-67</v>
+        <v>0</v>
       </c>
       <c r="J86" s="27">
         <v>0</v>
@@ -10745,105 +10744,105 @@
       <c r="L86" s="27"/>
       <c r="M86" s="20"/>
     </row>
-    <row r="87" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B87" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="27">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D87" s="27">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E87" s="27">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="F87" s="27">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G87" s="27">
-        <v>39</v>
+        <v>-10</v>
       </c>
       <c r="H87" s="27">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I87" s="27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J87" s="27">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K87" s="27"/>
       <c r="L87" s="27"/>
       <c r="M87" s="20"/>
     </row>
-    <row r="88" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B88" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C88" s="27">
-        <v>913</v>
+        <v>-661</v>
       </c>
       <c r="D88" s="27">
-        <v>-661</v>
+        <v>-2213</v>
       </c>
       <c r="E88" s="27">
-        <v>-2213</v>
+        <v>96</v>
       </c>
       <c r="F88" s="27">
-        <v>96</v>
+        <v>748</v>
       </c>
       <c r="G88" s="27">
-        <v>748</v>
+        <v>330</v>
       </c>
       <c r="H88" s="27">
-        <v>330</v>
+        <v>-1085</v>
       </c>
       <c r="I88" s="27">
-        <v>-1085</v>
+        <v>-114</v>
       </c>
       <c r="J88" s="27">
-        <v>-114</v>
+        <v>280</v>
       </c>
       <c r="K88" s="27"/>
       <c r="L88" s="27"/>
       <c r="M88" s="20"/>
     </row>
-    <row r="89" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B89" s="9" t="s">
         <v>58</v>
       </c>
       <c r="C89" s="27">
-        <v>-368</v>
+        <v>-342</v>
       </c>
       <c r="D89" s="27">
-        <v>-342</v>
+        <v>-386</v>
       </c>
       <c r="E89" s="27">
-        <v>-386</v>
+        <v>-362</v>
       </c>
       <c r="F89" s="27">
-        <v>-362</v>
+        <v>-682</v>
       </c>
       <c r="G89" s="27">
-        <v>-682</v>
+        <v>-261</v>
       </c>
       <c r="H89" s="27">
-        <v>-261</v>
+        <v>-636</v>
       </c>
       <c r="I89" s="27">
-        <v>-636</v>
+        <v>-610</v>
       </c>
       <c r="J89" s="27">
-        <v>-610</v>
+        <v>-125</v>
       </c>
       <c r="K89" s="27"/>
       <c r="L89" s="27"/>
       <c r="M89" s="20"/>
     </row>
-    <row r="90" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B90" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C90" s="27">
         <v>0</v>
@@ -10852,10 +10851,10 @@
         <v>0</v>
       </c>
       <c r="E90" s="27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F90" s="27">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G90" s="27">
         <v>0</v>
@@ -10873,105 +10872,105 @@
       <c r="L90" s="27"/>
       <c r="M90" s="20"/>
     </row>
-    <row r="91" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B91" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C91" s="27">
-        <v>-919</v>
+        <v>45</v>
       </c>
       <c r="D91" s="27">
-        <v>45</v>
+        <v>703</v>
       </c>
       <c r="E91" s="27">
-        <v>703</v>
+        <v>494</v>
       </c>
       <c r="F91" s="27">
-        <v>494</v>
+        <v>-237</v>
       </c>
       <c r="G91" s="27">
-        <v>-237</v>
+        <v>-140</v>
       </c>
       <c r="H91" s="27">
-        <v>-140</v>
+        <v>118</v>
       </c>
       <c r="I91" s="27">
-        <v>118</v>
+        <v>248</v>
       </c>
       <c r="J91" s="27">
-        <v>248</v>
+        <v>-308</v>
       </c>
       <c r="K91" s="27"/>
       <c r="L91" s="27"/>
       <c r="M91" s="20"/>
     </row>
-    <row r="92" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B92" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C92" s="27">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="D92" s="27">
-        <v>88</v>
+        <v>363</v>
       </c>
       <c r="E92" s="27">
-        <v>363</v>
+        <v>257</v>
       </c>
       <c r="F92" s="27">
-        <v>257</v>
+        <v>-288</v>
       </c>
       <c r="G92" s="27">
-        <v>-288</v>
+        <v>-301</v>
       </c>
       <c r="H92" s="27">
-        <v>-301</v>
+        <v>444</v>
       </c>
       <c r="I92" s="27">
-        <v>444</v>
+        <v>531</v>
       </c>
       <c r="J92" s="27">
-        <v>531</v>
+        <v>0</v>
       </c>
       <c r="K92" s="27"/>
       <c r="L92" s="27"/>
       <c r="M92" s="20"/>
     </row>
-    <row r="93" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B93" s="9" t="s">
         <v>59</v>
       </c>
       <c r="C93" s="27">
-        <v>-561</v>
+        <v>262</v>
       </c>
       <c r="D93" s="27">
-        <v>262</v>
+        <v>873</v>
       </c>
       <c r="E93" s="27">
-        <v>873</v>
+        <v>-585</v>
       </c>
       <c r="F93" s="27">
-        <v>-585</v>
+        <v>-289</v>
       </c>
       <c r="G93" s="27">
-        <v>-289</v>
+        <v>836</v>
       </c>
       <c r="H93" s="27">
-        <v>836</v>
+        <v>451</v>
       </c>
       <c r="I93" s="27">
-        <v>451</v>
+        <v>-588</v>
       </c>
       <c r="J93" s="27">
-        <v>-588</v>
+        <v>-104</v>
       </c>
       <c r="K93" s="27"/>
       <c r="L93" s="27"/>
       <c r="M93" s="20"/>
     </row>
-    <row r="94" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B94" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C94" s="27">
         <v>0</v>
@@ -10986,49 +10985,49 @@
         <v>0</v>
       </c>
       <c r="G94" s="27">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="H94" s="27">
-        <v>549</v>
+        <v>371</v>
       </c>
       <c r="I94" s="27">
-        <v>371</v>
+        <v>296</v>
       </c>
       <c r="J94" s="27">
-        <v>296</v>
+        <v>713</v>
       </c>
       <c r="K94" s="27"/>
       <c r="L94" s="27"/>
       <c r="M94" s="20"/>
     </row>
-    <row r="95" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7"/>
       <c r="B95" s="17" t="s">
         <v>60</v>
       </c>
       <c r="C95" s="55">
-        <v>521</v>
+        <v>593</v>
       </c>
       <c r="D95" s="55">
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="E95" s="55">
-        <v>628</v>
+        <v>1299</v>
       </c>
       <c r="F95" s="55">
-        <v>1299</v>
+        <v>939</v>
       </c>
       <c r="G95" s="55">
-        <v>939</v>
+        <v>2011</v>
       </c>
       <c r="H95" s="55">
-        <v>2011</v>
+        <v>2159</v>
       </c>
       <c r="I95" s="55">
-        <v>2159</v>
+        <v>2600</v>
       </c>
       <c r="J95" s="55">
-        <v>2600</v>
+        <v>2955</v>
       </c>
       <c r="K95" s="33"/>
       <c r="L95" s="33"/>
@@ -11036,137 +11035,137 @@
       <c r="O95" s="7"/>
       <c r="S95" s="7"/>
     </row>
-    <row r="96" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B96" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C96" s="27">
-        <v>-142</v>
+        <v>-154</v>
       </c>
       <c r="D96" s="27">
-        <v>-154</v>
+        <v>-132</v>
       </c>
       <c r="E96" s="27">
-        <v>-132</v>
+        <v>-208</v>
       </c>
       <c r="F96" s="27">
-        <v>-208</v>
+        <v>-212</v>
       </c>
       <c r="G96" s="27">
-        <v>-212</v>
+        <v>-282</v>
       </c>
       <c r="H96" s="27">
-        <v>-282</v>
+        <v>-258</v>
       </c>
       <c r="I96" s="27">
-        <v>-258</v>
+        <v>-222</v>
       </c>
       <c r="J96" s="27">
-        <v>-222</v>
+        <v>-389</v>
       </c>
       <c r="K96" s="27"/>
       <c r="L96" s="27"/>
       <c r="M96" s="20"/>
     </row>
-    <row r="97" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B97" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C97" s="27">
-        <v>-433</v>
+        <v>-132</v>
       </c>
       <c r="D97" s="27">
-        <v>-132</v>
+        <v>-142</v>
       </c>
       <c r="E97" s="27">
-        <v>-142</v>
+        <v>-786</v>
       </c>
       <c r="F97" s="27">
-        <v>-786</v>
+        <v>-304</v>
       </c>
       <c r="G97" s="27">
-        <v>-304</v>
+        <v>-492</v>
       </c>
       <c r="H97" s="27">
-        <v>-492</v>
+        <v>-1314</v>
       </c>
       <c r="I97" s="27">
-        <v>-1314</v>
+        <v>-3360</v>
       </c>
       <c r="J97" s="27">
-        <v>-3360</v>
+        <v>-2545</v>
       </c>
       <c r="K97" s="27"/>
       <c r="L97" s="27"/>
       <c r="M97" s="20"/>
     </row>
-    <row r="98" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B98" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C98" s="27">
-        <v>443</v>
+        <v>761</v>
       </c>
       <c r="D98" s="27">
-        <v>761</v>
+        <v>738</v>
       </c>
       <c r="E98" s="27">
-        <v>738</v>
+        <v>90</v>
       </c>
       <c r="F98" s="27">
-        <v>90</v>
+        <v>398</v>
       </c>
       <c r="G98" s="27">
-        <v>398</v>
+        <v>333</v>
       </c>
       <c r="H98" s="27">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="I98" s="27">
-        <v>317</v>
+        <v>797</v>
       </c>
       <c r="J98" s="27">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="K98" s="27"/>
       <c r="L98" s="27"/>
       <c r="M98" s="20"/>
     </row>
-    <row r="99" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B99" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C99" s="27">
         <v>0</v>
       </c>
       <c r="D99" s="27">
-        <v>0</v>
+        <v>-548</v>
       </c>
       <c r="E99" s="27">
-        <v>-548</v>
+        <v>0</v>
       </c>
       <c r="F99" s="27">
         <v>0</v>
       </c>
       <c r="G99" s="27">
-        <v>0</v>
+        <v>-1716</v>
       </c>
       <c r="H99" s="27">
-        <v>-1716</v>
+        <v>0</v>
       </c>
       <c r="I99" s="27">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="J99" s="27">
-        <v>-44</v>
+        <v>0</v>
       </c>
       <c r="K99" s="27"/>
       <c r="L99" s="27"/>
       <c r="M99" s="20"/>
     </row>
-    <row r="100" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B100" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C100" s="27">
         <v>0</v>
@@ -11196,9 +11195,9 @@
       <c r="L100" s="27"/>
       <c r="M100" s="20"/>
     </row>
-    <row r="101" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B101" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C101" s="27">
         <v>0</v>
@@ -11207,10 +11206,10 @@
         <v>0</v>
       </c>
       <c r="E101" s="27">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="27">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="27">
         <v>0</v>
@@ -11228,39 +11227,39 @@
       <c r="L101" s="27"/>
       <c r="M101" s="20"/>
     </row>
-    <row r="102" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B102" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C102" s="27">
-        <v>-4</v>
+        <v>-90</v>
       </c>
       <c r="D102" s="27">
-        <v>-90</v>
+        <v>-37</v>
       </c>
       <c r="E102" s="27">
-        <v>-37</v>
+        <v>-210</v>
       </c>
       <c r="F102" s="27">
-        <v>-210</v>
+        <v>-239</v>
       </c>
       <c r="G102" s="27">
-        <v>-239</v>
+        <v>-119</v>
       </c>
       <c r="H102" s="27">
-        <v>-119</v>
+        <v>-74</v>
       </c>
       <c r="I102" s="27">
-        <v>-74</v>
+        <v>-70</v>
       </c>
       <c r="J102" s="27">
-        <v>-70</v>
+        <v>-409</v>
       </c>
       <c r="K102" s="27"/>
       <c r="L102" s="27"/>
       <c r="M102" s="20"/>
     </row>
-    <row r="103" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B103" s="9" t="s">
         <v>56</v>
       </c>
@@ -11268,10 +11267,10 @@
         <v>1</v>
       </c>
       <c r="D103" s="27">
-        <v>1</v>
+        <v>-17</v>
       </c>
       <c r="E103" s="27">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="F103" s="27">
         <v>0</v>
@@ -11283,18 +11282,18 @@
         <v>0</v>
       </c>
       <c r="I103" s="27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J103" s="27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K103" s="27"/>
       <c r="L103" s="27"/>
       <c r="M103" s="20"/>
     </row>
-    <row r="104" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B104" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C104" s="27">
         <v>0</v>
@@ -11309,49 +11308,49 @@
         <v>0</v>
       </c>
       <c r="G104" s="27">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="H104" s="27">
-        <v>-22</v>
+        <v>-8</v>
       </c>
       <c r="I104" s="27">
-        <v>-8</v>
+        <v>1348</v>
       </c>
       <c r="J104" s="27">
-        <v>1348</v>
+        <v>0</v>
       </c>
       <c r="K104" s="27"/>
       <c r="L104" s="27"/>
       <c r="M104" s="20"/>
     </row>
-    <row r="105" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7"/>
       <c r="B105" s="17" t="s">
         <v>62</v>
       </c>
       <c r="C105" s="55">
-        <v>-135</v>
+        <v>386</v>
       </c>
       <c r="D105" s="55">
-        <v>386</v>
+        <v>-138</v>
       </c>
       <c r="E105" s="55">
-        <v>-138</v>
+        <v>-1214</v>
       </c>
       <c r="F105" s="55">
-        <v>-1214</v>
+        <v>-357</v>
       </c>
       <c r="G105" s="55">
-        <v>-357</v>
+        <v>-2298</v>
       </c>
       <c r="H105" s="55">
-        <v>-2298</v>
+        <v>-1337</v>
       </c>
       <c r="I105" s="55">
-        <v>-1337</v>
+        <v>-1541</v>
       </c>
       <c r="J105" s="55">
-        <v>-1541</v>
+        <v>-2565</v>
       </c>
       <c r="K105" s="33"/>
       <c r="L105" s="33"/>
@@ -11359,47 +11358,47 @@
       <c r="O105" s="7"/>
       <c r="S105" s="7"/>
     </row>
-    <row r="106" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B106" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C106" s="27">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="D106" s="27">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="E106" s="27">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="F106" s="27">
-        <v>127</v>
+        <v>2441</v>
       </c>
       <c r="G106" s="27">
-        <v>2441</v>
+        <v>155</v>
       </c>
       <c r="H106" s="27">
-        <v>155</v>
+        <v>10</v>
       </c>
       <c r="I106" s="27">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="J106" s="27">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="K106" s="27"/>
       <c r="L106" s="27"/>
       <c r="M106" s="20"/>
     </row>
-    <row r="107" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B107" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C107" s="27">
-        <v>0</v>
+        <v>-750</v>
       </c>
       <c r="D107" s="27">
-        <v>-750</v>
+        <v>0</v>
       </c>
       <c r="E107" s="27">
         <v>0</v>
@@ -11408,10 +11407,10 @@
         <v>0</v>
       </c>
       <c r="G107" s="27">
-        <v>0</v>
+        <v>-950</v>
       </c>
       <c r="H107" s="27">
-        <v>-950</v>
+        <v>0</v>
       </c>
       <c r="I107" s="27">
         <v>0</v>
@@ -11423,44 +11422,44 @@
       <c r="L107" s="27"/>
       <c r="M107" s="20"/>
     </row>
-    <row r="108" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B108" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C108" s="27">
-        <v>-4</v>
+        <v>-352</v>
       </c>
       <c r="D108" s="27">
-        <v>-352</v>
+        <v>-250</v>
       </c>
       <c r="E108" s="27">
-        <v>-250</v>
+        <v>-256</v>
       </c>
       <c r="F108" s="27">
-        <v>-256</v>
+        <v>-749</v>
       </c>
       <c r="G108" s="27">
-        <v>-749</v>
+        <v>-478</v>
       </c>
       <c r="H108" s="27">
-        <v>-478</v>
+        <v>-89</v>
       </c>
       <c r="I108" s="27">
-        <v>-89</v>
+        <v>0</v>
       </c>
       <c r="J108" s="27">
-        <v>0</v>
+        <v>-221</v>
       </c>
       <c r="K108" s="27"/>
       <c r="L108" s="27"/>
       <c r="M108" s="20"/>
     </row>
-    <row r="109" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B109" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C109" s="27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D109" s="27">
         <v>0</v>
@@ -11469,10 +11468,10 @@
         <v>0</v>
       </c>
       <c r="F109" s="27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G109" s="27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H109" s="27">
         <v>0</v>
@@ -11487,44 +11486,44 @@
       <c r="L109" s="27"/>
       <c r="M109" s="20"/>
     </row>
-    <row r="110" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B110" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C110" s="27">
-        <v>-129</v>
+        <v>-97</v>
       </c>
       <c r="D110" s="27">
-        <v>-97</v>
+        <v>-460</v>
       </c>
       <c r="E110" s="27">
-        <v>-460</v>
+        <v>-42</v>
       </c>
       <c r="F110" s="27">
-        <v>-42</v>
+        <v>-30</v>
       </c>
       <c r="G110" s="27">
-        <v>-30</v>
+        <v>-46</v>
       </c>
       <c r="H110" s="27">
-        <v>-46</v>
+        <v>-371</v>
       </c>
       <c r="I110" s="27">
-        <v>-371</v>
+        <v>-160</v>
       </c>
       <c r="J110" s="27">
-        <v>-160</v>
+        <v>-134</v>
       </c>
       <c r="K110" s="27"/>
       <c r="L110" s="27"/>
       <c r="M110" s="20"/>
     </row>
-    <row r="111" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B111" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C111" s="27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D111" s="27">
         <v>0</v>
@@ -11542,43 +11541,43 @@
         <v>0</v>
       </c>
       <c r="I111" s="27">
-        <v>0</v>
+        <v>-284</v>
       </c>
       <c r="J111" s="27">
-        <v>-284</v>
+        <v>0</v>
       </c>
       <c r="K111" s="27"/>
       <c r="L111" s="27"/>
       <c r="M111" s="20"/>
     </row>
-    <row r="112" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7"/>
       <c r="B112" s="17" t="s">
         <v>64</v>
       </c>
       <c r="C112" s="55">
-        <v>-129</v>
+        <v>-1056</v>
       </c>
       <c r="D112" s="55">
-        <v>-1056</v>
+        <v>-706</v>
       </c>
       <c r="E112" s="55">
-        <v>-706</v>
+        <v>-171</v>
       </c>
       <c r="F112" s="55">
-        <v>-171</v>
+        <v>1666</v>
       </c>
       <c r="G112" s="55">
-        <v>1666</v>
+        <v>-1319</v>
       </c>
       <c r="H112" s="55">
-        <v>-1319</v>
+        <v>-450</v>
       </c>
       <c r="I112" s="55">
-        <v>-450</v>
+        <v>-328</v>
       </c>
       <c r="J112" s="55">
-        <v>-328</v>
+        <v>-350</v>
       </c>
       <c r="K112" s="33"/>
       <c r="L112" s="33"/>
@@ -11586,7 +11585,7 @@
       <c r="O112" s="7"/>
       <c r="S112" s="7"/>
     </row>
-    <row r="113" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B113" s="9" t="s">
         <v>65</v>
       </c>
@@ -11618,98 +11617,98 @@
       <c r="L113" s="27"/>
       <c r="M113" s="20"/>
     </row>
-    <row r="114" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B114" s="11" t="s">
         <v>66</v>
       </c>
       <c r="C114" s="59">
-        <v>257</v>
+        <v>-77</v>
       </c>
       <c r="D114" s="59">
-        <v>-77</v>
+        <v>-216</v>
       </c>
       <c r="E114" s="59">
-        <v>-216</v>
+        <v>-86</v>
       </c>
       <c r="F114" s="59">
-        <v>-86</v>
+        <v>2248</v>
       </c>
       <c r="G114" s="59">
-        <v>2248</v>
+        <v>-1606</v>
       </c>
       <c r="H114" s="59">
-        <v>-1606</v>
+        <v>372</v>
       </c>
       <c r="I114" s="59">
-        <v>372</v>
+        <v>731</v>
       </c>
       <c r="J114" s="59">
-        <v>731</v>
+        <v>40</v>
       </c>
       <c r="K114" s="33"/>
       <c r="L114" s="33"/>
       <c r="M114" s="21"/>
     </row>
-    <row r="115" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:19" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B115" s="11" t="s">
         <v>67</v>
       </c>
       <c r="C115" s="59">
-        <v>3933</v>
+        <v>4190</v>
       </c>
       <c r="D115" s="59">
-        <v>4190</v>
+        <v>4113</v>
       </c>
       <c r="E115" s="59">
-        <v>4113</v>
+        <v>3897</v>
       </c>
       <c r="F115" s="59">
-        <v>3897</v>
+        <v>3811</v>
       </c>
       <c r="G115" s="59">
-        <v>3811</v>
+        <v>6059</v>
       </c>
       <c r="H115" s="59">
-        <v>6059</v>
+        <v>4453</v>
       </c>
       <c r="I115" s="59">
-        <v>4453</v>
+        <v>4825</v>
       </c>
       <c r="J115" s="59">
-        <v>4825</v>
+        <v>5556</v>
       </c>
       <c r="K115" s="21"/>
       <c r="L115" s="21"/>
       <c r="M115" s="21"/>
     </row>
-    <row r="116" spans="1:19" s="13" customFormat="1" ht="17" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" s="13" customFormat="1" ht="17" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A116" s="7"/>
       <c r="B116" s="19" t="s">
         <v>68</v>
       </c>
       <c r="C116" s="55">
-        <v>4190</v>
+        <v>4113</v>
       </c>
       <c r="D116" s="55">
-        <v>4113</v>
+        <v>3897</v>
       </c>
       <c r="E116" s="55">
-        <v>3897</v>
+        <v>3811</v>
       </c>
       <c r="F116" s="55">
-        <v>3811</v>
+        <v>6059</v>
       </c>
       <c r="G116" s="55">
-        <v>6059</v>
+        <v>4453</v>
       </c>
       <c r="H116" s="55">
-        <v>4453</v>
+        <v>4825</v>
       </c>
       <c r="I116" s="55">
-        <v>4825</v>
+        <v>5556</v>
       </c>
       <c r="J116" s="55">
-        <v>5556</v>
+        <v>5596</v>
       </c>
       <c r="K116" s="21"/>
       <c r="L116" s="21"/>
@@ -11717,7 +11716,7 @@
       <c r="O116" s="7"/>
       <c r="S116" s="7"/>
     </row>
-    <row r="117" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B117" s="1"/>
     </row>
     <row r="118" spans="1:19" s="14" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -11736,48 +11735,48 @@
         <v>70</v>
       </c>
       <c r="C119" s="20">
-        <f t="shared" ref="C119:I119" si="18">C5-C6-C7-C15+C17+C18+C20+C21</f>
-        <v>123</v>
+        <f t="shared" ref="C119:H119" si="18">C5-C6-C7-C15+C17+C18+C20+C21</f>
+        <v>265</v>
       </c>
       <c r="D119" s="20">
         <f t="shared" si="18"/>
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="E119" s="20">
         <f t="shared" si="18"/>
-        <v>771</v>
+        <v>482</v>
       </c>
       <c r="F119" s="20">
         <f t="shared" si="18"/>
-        <v>482</v>
+        <v>709</v>
       </c>
       <c r="G119" s="20">
         <f t="shared" si="18"/>
-        <v>709</v>
+        <v>768</v>
       </c>
       <c r="H119" s="20">
         <f t="shared" si="18"/>
-        <v>768</v>
+        <v>1172</v>
       </c>
       <c r="I119" s="20">
-        <f t="shared" si="18"/>
-        <v>1172</v>
+        <f t="shared" ref="I119:J119" si="19">I5-I6-I7-I15+I17+I18+I20+I21</f>
+        <v>1620</v>
       </c>
       <c r="J119" s="20">
-        <f t="shared" ref="J119" si="19">J5-J6-J7-J15+J17+J18+J20+J21</f>
-        <v>1620</v>
+        <f t="shared" si="19"/>
+        <v>1372</v>
       </c>
       <c r="K119" s="20"/>
       <c r="L119" s="20"/>
       <c r="M119" s="20"/>
     </row>
-    <row r="120" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:19" s="18" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A120" s="7"/>
       <c r="B120" s="17" t="s">
         <v>71</v>
       </c>
       <c r="C120" s="24">
-        <f t="shared" ref="C120:I120" si="20">C22-C119</f>
+        <f t="shared" ref="C120:H120" si="20">C22-C119</f>
         <v>0</v>
       </c>
       <c r="D120" s="24">
@@ -11801,11 +11800,11 @@
         <v>0</v>
       </c>
       <c r="I120" s="24">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="I120:J120" si="21">I22-I119</f>
         <v>0</v>
       </c>
       <c r="J120" s="24">
-        <f t="shared" ref="J120" si="21">J22-J119</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K120" s="26"/>
@@ -11819,47 +11818,47 @@
         <v>72</v>
       </c>
       <c r="C121" s="20">
-        <f t="shared" ref="C121:I121" si="22">SUM(C33:C40)+SUM(C42:C48)</f>
-        <v>67895</v>
+        <f t="shared" ref="C121:H121" si="22">SUM(C33:C40)+SUM(C42:C48)</f>
+        <v>67886</v>
       </c>
       <c r="D121" s="20">
         <f t="shared" si="22"/>
-        <v>67886</v>
+        <v>69636</v>
       </c>
       <c r="E121" s="20">
         <f t="shared" si="22"/>
-        <v>69636</v>
+        <v>69226</v>
       </c>
       <c r="F121" s="20">
         <f t="shared" si="22"/>
-        <v>69226</v>
+        <v>71550</v>
       </c>
       <c r="G121" s="20">
         <f t="shared" si="22"/>
-        <v>71550</v>
+        <v>74820</v>
       </c>
       <c r="H121" s="20">
         <f t="shared" si="22"/>
-        <v>74820</v>
+        <v>76891</v>
       </c>
       <c r="I121" s="20">
-        <f t="shared" si="22"/>
-        <v>76891</v>
+        <f t="shared" ref="I121:J121" si="23">SUM(I33:I40)+SUM(I42:I48)</f>
+        <v>76926</v>
       </c>
       <c r="J121" s="20">
-        <f t="shared" ref="J121" si="23">SUM(J33:J40)+SUM(J42:J48)</f>
-        <v>76926</v>
+        <f t="shared" si="23"/>
+        <v>79642</v>
       </c>
       <c r="K121" s="20"/>
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
     </row>
-    <row r="122" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B122" s="11" t="s">
         <v>73</v>
       </c>
       <c r="C122" s="23">
-        <f t="shared" ref="C122:I122" si="24">C50-C121</f>
+        <f t="shared" ref="C122:H122" si="24">C50-C121</f>
         <v>0</v>
       </c>
       <c r="D122" s="23">
@@ -11883,11 +11882,11 @@
         <v>0</v>
       </c>
       <c r="I122" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="I122:J122" si="25">I50-I121</f>
         <v>0</v>
       </c>
       <c r="J122" s="23">
-        <f t="shared" ref="J122" si="25">J50-J121</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K122" s="26"/>
@@ -11899,47 +11898,47 @@
         <v>74</v>
       </c>
       <c r="C123" s="20">
-        <f t="shared" ref="C123:I123" si="26">SUM(C51:C57)+SUM(C59:C62)</f>
-        <v>11697</v>
+        <f t="shared" ref="C123:H123" si="26">SUM(C51:C57)+SUM(C59:C62)</f>
+        <v>11348</v>
       </c>
       <c r="D123" s="20">
         <f t="shared" si="26"/>
-        <v>11348</v>
+        <v>12651</v>
       </c>
       <c r="E123" s="20">
         <f t="shared" si="26"/>
-        <v>12651</v>
+        <v>11658</v>
       </c>
       <c r="F123" s="20">
         <f t="shared" si="26"/>
-        <v>11658</v>
+        <v>13669</v>
       </c>
       <c r="G123" s="20">
         <f t="shared" si="26"/>
-        <v>13669</v>
+        <v>15155</v>
       </c>
       <c r="H123" s="20">
         <f t="shared" si="26"/>
-        <v>15155</v>
+        <v>16101</v>
       </c>
       <c r="I123" s="20">
-        <f t="shared" si="26"/>
-        <v>16101</v>
+        <f t="shared" ref="I123:J123" si="27">SUM(I51:I57)+SUM(I59:I62)</f>
+        <v>13927</v>
       </c>
       <c r="J123" s="20">
-        <f t="shared" ref="J123" si="27">SUM(J51:J57)+SUM(J59:J62)</f>
-        <v>13927</v>
+        <f t="shared" si="27"/>
+        <v>15180</v>
       </c>
       <c r="K123" s="20"/>
       <c r="L123" s="20"/>
       <c r="M123" s="20"/>
     </row>
-    <row r="124" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B124" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C124" s="23">
-        <f t="shared" ref="C124:I124" si="28">C64-C123</f>
+        <f t="shared" ref="C124:H124" si="28">C64-C123</f>
         <v>0</v>
       </c>
       <c r="D124" s="23">
@@ -11963,11 +11962,11 @@
         <v>0</v>
       </c>
       <c r="I124" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="I124:J124" si="29">I64-I123</f>
         <v>0</v>
       </c>
       <c r="J124" s="23">
-        <f t="shared" ref="J124" si="29">J64-J123</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="K124" s="26"/>
@@ -11979,47 +11978,47 @@
         <v>76</v>
       </c>
       <c r="C125" s="20">
-        <f t="shared" ref="C125:I125" si="30">SUM(C65:C69)+C71</f>
-        <v>56198</v>
+        <f t="shared" ref="C125:H125" si="30">SUM(C65:C69)+C71</f>
+        <v>56538</v>
       </c>
       <c r="D125" s="20">
         <f t="shared" si="30"/>
-        <v>56538</v>
+        <v>56985</v>
       </c>
       <c r="E125" s="20">
         <f t="shared" si="30"/>
-        <v>56985</v>
+        <v>57568</v>
       </c>
       <c r="F125" s="20">
         <f t="shared" si="30"/>
-        <v>57568</v>
+        <v>57881</v>
       </c>
       <c r="G125" s="20">
         <f t="shared" si="30"/>
-        <v>57881</v>
+        <v>59665</v>
       </c>
       <c r="H125" s="20">
         <f t="shared" si="30"/>
-        <v>59665</v>
+        <v>60790</v>
       </c>
       <c r="I125" s="20">
-        <f t="shared" si="30"/>
-        <v>60790</v>
+        <f t="shared" ref="I125:J125" si="31">SUM(I65:I69)+I71</f>
+        <v>62999</v>
       </c>
       <c r="J125" s="20">
-        <f t="shared" ref="J125" si="31">SUM(J65:J69)+J71</f>
-        <v>62999</v>
+        <f t="shared" si="31"/>
+        <v>64462</v>
       </c>
       <c r="K125" s="20"/>
       <c r="L125" s="20"/>
       <c r="M125" s="20"/>
     </row>
-    <row r="126" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B126" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C126" s="23">
-        <f t="shared" ref="C126:I126" si="32">C72-C125</f>
+        <f t="shared" ref="C126:H126" si="32">C72-C125</f>
         <v>0</v>
       </c>
       <c r="D126" s="23">
@@ -12043,24 +12042,24 @@
         <v>0</v>
       </c>
       <c r="I126" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="I126:J126" si="33">I72-I125</f>
         <v>0</v>
       </c>
       <c r="J126" s="23">
-        <f t="shared" ref="J126" si="33">J72-J125</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K126" s="26"/>
       <c r="L126" s="26"/>
       <c r="M126" s="26"/>
     </row>
-    <row r="127" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:19" s="18" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="17" t="s">
         <v>87</v>
       </c>
       <c r="C127" s="22">
-        <f t="shared" ref="C127:I127" si="34">C50-(C64+C72)</f>
+        <f t="shared" ref="C127:H127" si="34">C50-(C64+C72)</f>
         <v>0</v>
       </c>
       <c r="D127" s="22">
@@ -12084,11 +12083,11 @@
         <v>0</v>
       </c>
       <c r="I127" s="22">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="I127:J127" si="35">I50-(I64+I72)</f>
         <v>0</v>
       </c>
       <c r="J127" s="22">
-        <f t="shared" ref="J127" si="35">J50-(J64+J72)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="K127" s="26"/>
@@ -12102,47 +12101,47 @@
         <v>78</v>
       </c>
       <c r="C128" s="20">
-        <f t="shared" ref="C128:I128" si="36">SUM(C76:C94)</f>
-        <v>521</v>
+        <f t="shared" ref="C128:H128" si="36">SUM(C76:C94)</f>
+        <v>593</v>
       </c>
       <c r="D128" s="20">
         <f t="shared" si="36"/>
-        <v>593</v>
+        <v>628</v>
       </c>
       <c r="E128" s="20">
         <f t="shared" si="36"/>
-        <v>628</v>
+        <v>1299</v>
       </c>
       <c r="F128" s="20">
         <f t="shared" si="36"/>
-        <v>1299</v>
+        <v>939</v>
       </c>
       <c r="G128" s="20">
         <f t="shared" si="36"/>
-        <v>939</v>
+        <v>2011</v>
       </c>
       <c r="H128" s="20">
         <f t="shared" si="36"/>
-        <v>2011</v>
+        <v>2159</v>
       </c>
       <c r="I128" s="20">
-        <f t="shared" si="36"/>
-        <v>2159</v>
+        <f t="shared" ref="I128:J128" si="37">SUM(I76:I94)</f>
+        <v>2600</v>
       </c>
       <c r="J128" s="20">
-        <f t="shared" ref="J128" si="37">SUM(J76:J94)</f>
-        <v>2600</v>
+        <f t="shared" si="37"/>
+        <v>2955</v>
       </c>
       <c r="K128" s="20"/>
       <c r="L128" s="20"/>
       <c r="M128" s="20"/>
     </row>
-    <row r="129" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B129" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C129" s="23">
-        <f t="shared" ref="C129:I129" si="38">C95-C128</f>
+        <f t="shared" ref="C129:H129" si="38">C95-C128</f>
         <v>0</v>
       </c>
       <c r="D129" s="23">
@@ -12166,11 +12165,11 @@
         <v>0</v>
       </c>
       <c r="I129" s="23">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="I129:J129" si="39">I95-I128</f>
         <v>0</v>
       </c>
       <c r="J129" s="23">
-        <f t="shared" ref="J129" si="39">J95-J128</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K129" s="26"/>
@@ -12182,47 +12181,47 @@
         <v>80</v>
       </c>
       <c r="C130" s="20">
-        <f t="shared" ref="C130:I130" si="40">SUM(C96:C104)</f>
-        <v>-135</v>
+        <f t="shared" ref="C130:H130" si="40">SUM(C96:C104)</f>
+        <v>386</v>
       </c>
       <c r="D130" s="20">
         <f t="shared" si="40"/>
-        <v>386</v>
+        <v>-138</v>
       </c>
       <c r="E130" s="20">
         <f t="shared" si="40"/>
-        <v>-138</v>
+        <v>-1214</v>
       </c>
       <c r="F130" s="20">
         <f t="shared" si="40"/>
-        <v>-1214</v>
+        <v>-357</v>
       </c>
       <c r="G130" s="20">
         <f t="shared" si="40"/>
-        <v>-357</v>
+        <v>-2298</v>
       </c>
       <c r="H130" s="20">
         <f t="shared" si="40"/>
-        <v>-2298</v>
+        <v>-1337</v>
       </c>
       <c r="I130" s="20">
-        <f t="shared" si="40"/>
-        <v>-1337</v>
+        <f t="shared" ref="I130:J130" si="41">SUM(I96:I104)</f>
+        <v>-1541</v>
       </c>
       <c r="J130" s="20">
-        <f t="shared" ref="J130" si="41">SUM(J96:J104)</f>
-        <v>-1541</v>
+        <f t="shared" si="41"/>
+        <v>-2565</v>
       </c>
       <c r="K130" s="20"/>
       <c r="L130" s="20"/>
       <c r="M130" s="20"/>
     </row>
-    <row r="131" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B131" s="11" t="s">
         <v>81</v>
       </c>
       <c r="C131" s="23">
-        <f t="shared" ref="C131:I131" si="42">C105-C130</f>
+        <f t="shared" ref="C131:H131" si="42">C105-C130</f>
         <v>0</v>
       </c>
       <c r="D131" s="23">
@@ -12246,11 +12245,11 @@
         <v>0</v>
       </c>
       <c r="I131" s="23">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="I131:J131" si="43">I105-I130</f>
         <v>0</v>
       </c>
       <c r="J131" s="23">
-        <f t="shared" ref="J131" si="43">J105-J130</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K131" s="26"/>
@@ -12262,47 +12261,47 @@
         <v>82</v>
       </c>
       <c r="C132" s="20">
-        <f t="shared" ref="C132:I132" si="44">SUM(C106:C111)</f>
-        <v>-129</v>
+        <f t="shared" ref="C132:H132" si="44">SUM(C106:C111)</f>
+        <v>-1056</v>
       </c>
       <c r="D132" s="20">
         <f t="shared" si="44"/>
-        <v>-1056</v>
+        <v>-706</v>
       </c>
       <c r="E132" s="20">
         <f t="shared" si="44"/>
-        <v>-706</v>
+        <v>-171</v>
       </c>
       <c r="F132" s="20">
         <f t="shared" si="44"/>
-        <v>-171</v>
+        <v>1666</v>
       </c>
       <c r="G132" s="20">
         <f t="shared" si="44"/>
-        <v>1666</v>
+        <v>-1319</v>
       </c>
       <c r="H132" s="20">
         <f t="shared" si="44"/>
-        <v>-1319</v>
+        <v>-450</v>
       </c>
       <c r="I132" s="20">
-        <f t="shared" si="44"/>
-        <v>-450</v>
+        <f t="shared" ref="I132:J132" si="45">SUM(I106:I111)</f>
+        <v>-328</v>
       </c>
       <c r="J132" s="20">
-        <f t="shared" ref="J132" si="45">SUM(J106:J111)</f>
-        <v>-328</v>
+        <f t="shared" si="45"/>
+        <v>-350</v>
       </c>
       <c r="K132" s="20"/>
       <c r="L132" s="20"/>
       <c r="M132" s="20"/>
     </row>
-    <row r="133" spans="1:19" s="7" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:19" s="7" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="B133" s="11" t="s">
         <v>83</v>
       </c>
       <c r="C133" s="23">
-        <f t="shared" ref="C133:I133" si="46">C112-C132</f>
+        <f t="shared" ref="C133:H133" si="46">C112-C132</f>
         <v>0</v>
       </c>
       <c r="D133" s="23">
@@ -12326,11 +12325,11 @@
         <v>0</v>
       </c>
       <c r="I133" s="23">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="I133:J133" si="47">I112-I132</f>
         <v>0</v>
       </c>
       <c r="J133" s="23">
-        <f t="shared" ref="J133" si="47">J112-J132</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K133" s="26"/>
@@ -12342,48 +12341,48 @@
         <v>85</v>
       </c>
       <c r="C134" s="20">
-        <f t="shared" ref="C134:I134" si="48">C95+C105+C112+C113+C115</f>
-        <v>4190</v>
+        <f t="shared" ref="C134:H134" si="48">C95+C105+C112+C113+C115</f>
+        <v>4113</v>
       </c>
       <c r="D134" s="20">
         <f t="shared" si="48"/>
-        <v>4113</v>
+        <v>3897</v>
       </c>
       <c r="E134" s="20">
         <f t="shared" si="48"/>
-        <v>3897</v>
+        <v>3811</v>
       </c>
       <c r="F134" s="20">
         <f t="shared" si="48"/>
-        <v>3811</v>
+        <v>6059</v>
       </c>
       <c r="G134" s="20">
         <f t="shared" si="48"/>
-        <v>6059</v>
+        <v>4453</v>
       </c>
       <c r="H134" s="20">
         <f t="shared" si="48"/>
-        <v>4453</v>
+        <v>4825</v>
       </c>
       <c r="I134" s="20">
-        <f t="shared" si="48"/>
-        <v>4825</v>
+        <f t="shared" ref="I134:J134" si="49">I95+I105+I112+I113+I115</f>
+        <v>5556</v>
       </c>
       <c r="J134" s="20">
-        <f t="shared" ref="J134" si="49">J95+J105+J112+J113+J115</f>
-        <v>5556</v>
+        <f t="shared" si="49"/>
+        <v>5596</v>
       </c>
       <c r="K134" s="20"/>
       <c r="L134" s="20"/>
       <c r="M134" s="20"/>
     </row>
-    <row r="135" spans="1:19" s="18" customFormat="1" hidden="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:19" s="18" customFormat="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="17" t="s">
         <v>84</v>
       </c>
       <c r="C135" s="22">
-        <f t="shared" ref="C135:I135" si="50">C116-C134</f>
+        <f t="shared" ref="C135:H135" si="50">C116-C134</f>
         <v>0</v>
       </c>
       <c r="D135" s="22">
@@ -12407,11 +12406,11 @@
         <v>0</v>
       </c>
       <c r="I135" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" ref="I135:J135" si="51">I116-I134</f>
         <v>0</v>
       </c>
       <c r="J135" s="22">
-        <f t="shared" ref="J135" si="51">J116-J134</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="K135" s="26"/>
@@ -12420,8 +12419,9 @@
       <c r="O135" s="7"/>
       <c r="S135" s="7"/>
     </row>
-    <row r="136" spans="1:19" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B136" s="8"/>
+      <c r="D136" s="8"/>
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
@@ -12448,28 +12448,28 @@
         <v>4</v>
       </c>
       <c r="C138" s="27">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D138" s="27">
-        <v>1618</v>
+        <v>1623</v>
       </c>
       <c r="E138" s="27">
+        <v>1620</v>
+      </c>
+      <c r="F138" s="27">
+        <v>1621</v>
+      </c>
+      <c r="G138" s="27">
         <v>1623</v>
       </c>
-      <c r="F138" s="27">
-        <v>1620</v>
-      </c>
-      <c r="G138" s="27">
-        <v>1621</v>
-      </c>
       <c r="H138" s="27">
-        <v>1623</v>
+        <v>1628</v>
       </c>
       <c r="I138" s="27">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="J138" s="27">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="K138" s="20"/>
       <c r="L138" s="20"/>
@@ -12477,7 +12477,7 @@
     </row>
     <row r="139" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B139" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C139" s="28">
         <v>0</v>
@@ -12513,7 +12513,7 @@
     <row r="141" spans="1:19" s="66" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C141" s="68"/>
       <c r="D141" s="68"/>
@@ -12529,104 +12529,104 @@
       <c r="O141" s="4"/>
       <c r="S141" s="4"/>
     </row>
-    <row r="142" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B142" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C142" s="27">
+        <v>6400</v>
+      </c>
+      <c r="D142" s="27">
+        <v>7200</v>
+      </c>
+      <c r="E142" s="27">
+        <v>6800</v>
+      </c>
+      <c r="F142" s="27">
+        <v>7100</v>
+      </c>
+      <c r="G142" s="27">
+        <v>8400</v>
+      </c>
+      <c r="H142" s="27">
+        <v>9300</v>
+      </c>
+      <c r="I142" s="27">
+        <v>9500</v>
+      </c>
+      <c r="J142" s="27">
+        <v>10900</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B143" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C142" s="27">
-        <v>5400</v>
-      </c>
-      <c r="D142" s="27">
-        <v>6400</v>
-      </c>
-      <c r="E142" s="27">
-        <v>7200</v>
-      </c>
-      <c r="F142" s="27">
-        <v>6800</v>
-      </c>
-      <c r="G142" s="27">
-        <v>7100</v>
-      </c>
-      <c r="H142" s="27">
-        <v>8400</v>
-      </c>
-      <c r="I142" s="27">
-        <v>9300</v>
-      </c>
-      <c r="J142" s="27">
-        <v>9500</v>
-      </c>
-    </row>
-    <row r="143" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="B143" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="C143" s="27">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="D143" s="27">
-        <v>7000</v>
+        <v>7800</v>
       </c>
       <c r="E143" s="27">
-        <v>7800</v>
+        <v>7400</v>
       </c>
       <c r="F143" s="27">
-        <v>7400</v>
+        <v>7700</v>
       </c>
       <c r="G143" s="27">
-        <v>7700</v>
+        <v>9000</v>
       </c>
       <c r="H143" s="27">
-        <v>9000</v>
+        <v>9900</v>
       </c>
       <c r="I143" s="27">
-        <v>9900</v>
+        <v>10100</v>
       </c>
       <c r="J143" s="27">
-        <v>10100</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B144" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C144" s="36">
         <f t="shared" ref="C144" si="52">D5</f>
-        <v>5835</v>
+        <v>6819</v>
       </c>
       <c r="D144" s="36">
         <f t="shared" ref="D144" si="53">E5</f>
-        <v>6819</v>
+        <v>7658</v>
       </c>
       <c r="E144" s="36">
         <f t="shared" ref="E144" si="54">F5</f>
-        <v>7658</v>
+        <v>7438</v>
       </c>
       <c r="F144" s="36">
         <f t="shared" ref="F144" si="55">G5</f>
-        <v>7438</v>
+        <v>7685</v>
       </c>
       <c r="G144" s="36">
         <f t="shared" ref="G144" si="56">H5</f>
-        <v>7685</v>
+        <v>9246</v>
       </c>
       <c r="H144" s="36">
         <f t="shared" ref="H144" si="57">I5</f>
-        <v>9246</v>
+        <v>10270</v>
       </c>
       <c r="I144" s="36">
         <f t="shared" ref="I144" si="58">J5</f>
-        <v>10270</v>
+        <v>10253</v>
       </c>
       <c r="J144" s="36">
         <f t="shared" ref="J144" si="59">K5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B145" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C145" s="93" t="str">
         <f t="shared" ref="C145" si="60">IF(D5&gt;C143, "BEAT", IF(D5&lt;C142, "MISSED", "MET"))</f>
@@ -12638,15 +12638,15 @@
       </c>
       <c r="E145" s="93" t="str">
         <f t="shared" ref="E145" si="62">IF(F5&gt;E143, "BEAT", IF(F5&lt;E142, "MISSED", "MET"))</f>
-        <v>MET</v>
+        <v>BEAT</v>
       </c>
       <c r="F145" s="93" t="str">
         <f t="shared" ref="F145" si="63">IF(G5&gt;F143, "BEAT", IF(G5&lt;F142, "MISSED", "MET"))</f>
-        <v>BEAT</v>
+        <v>MET</v>
       </c>
       <c r="G145" s="93" t="str">
         <f t="shared" ref="G145" si="64">IF(H5&gt;G143, "BEAT", IF(H5&lt;G142, "MISSED", "MET"))</f>
-        <v>MET</v>
+        <v>BEAT</v>
       </c>
       <c r="H145" s="93" t="str">
         <f t="shared" ref="H145" si="65">IF(I5&gt;H143, "BEAT", IF(I5&lt;H142, "MISSED", "MET"))</f>
@@ -12661,9 +12661,9 @@
         <v>MISSED</v>
       </c>
     </row>
-    <row r="146" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B146" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C146" s="31"/>
       <c r="D146" s="31"/>
@@ -12674,9 +12674,9 @@
       <c r="I146" s="31"/>
       <c r="J146" s="31"/>
     </row>
-    <row r="147" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B147" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C147" s="31"/>
       <c r="D147" s="31"/>
@@ -12687,9 +12687,9 @@
       <c r="I147" s="31"/>
       <c r="J147" s="31"/>
     </row>
-    <row r="148" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B148" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C148" s="25"/>
       <c r="D148" s="25"/>
@@ -12703,9 +12703,9 @@
       <c r="L148" s="20"/>
       <c r="M148" s="20"/>
     </row>
-    <row r="149" spans="2:13" hidden="1" outlineLevel="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:13" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B149" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C149" s="67"/>
       <c r="D149" s="67"/>
@@ -12719,7 +12719,6 @@
       <c r="L149" s="8"/>
       <c r="M149" s="8"/>
     </row>
-    <row r="150" spans="2:13" collapsed="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="P4:R4"/>
@@ -12727,7 +12726,7 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="J63 J130 J132 J49 N7 N14 N22:N28 N5:N6 N9:N10 N16:N21 N11:N13 C63:I63 C49:I49" formulaRange="1"/>
+    <ignoredError sqref="J63 J130 J132 J49 N7 N14 N22:N28 N5:N6 N9:N10 N16:N21 N11:N13" formulaRange="1"/>
     <ignoredError sqref="R6" formula="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>

--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72BD642-7E06-8F4E-8DD4-4454A9F7314A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5EC9E1A-DF79-B748-89AD-B7770E513D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="2" r:id="rId1"/>
@@ -1184,7 +1184,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="C3">
-            <v>405.47500000000002</v>
+            <v>510.13</v>
           </cell>
         </row>
       </sheetData>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C3" s="38">
         <f>[1]Sheet1!$C$3</f>
-        <v>405.47500000000002</v>
+        <v>510.13</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="C9" s="94">
         <f>C3*'Statement Q'!J138</f>
-        <v>661329.72500000009</v>
+        <v>832022.03</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
